--- a/research/traditional_assets/database/data/lithuania/lithuania_diversified.xlsx
+++ b/research/traditional_assets/database/data/lithuania/lithuania_diversified.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08555941899599918</v>
+        <v>0.08546932986750518</v>
       </c>
       <c r="C2">
-        <v>245.742921430205</v>
+        <v>243.4591340637374</v>
       </c>
       <c r="D2">
-        <v>242.392921430205</v>
+        <v>242.5671340637374</v>
       </c>
       <c r="E2">
-        <v>-11.9</v>
+        <v>-9.442</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.458</v>
       </c>
       <c r="G2">
         <v>3.35</v>
@@ -1451,28 +1451,28 @@
         <v>36.448</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1236374</v>
       </c>
       <c r="N2">
-        <v>36.448</v>
+        <v>36.3243626</v>
       </c>
       <c r="O2">
-        <v>5.4672</v>
+        <v>5.44865439</v>
       </c>
       <c r="P2">
-        <v>30.9808</v>
+        <v>30.87570821</v>
       </c>
       <c r="Q2">
-        <v>31.8328</v>
+        <v>31.72770821</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08555941899599918</v>
+        <v>0.08590078774495473</v>
       </c>
       <c r="T2">
-        <v>0.7282077218429368</v>
+        <v>0.7344600103638105</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>294.7975289030665</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08546932986750518</v>
+        <v>0.08537924073901118</v>
       </c>
       <c r="C3">
-        <v>243.4591340637374</v>
+        <v>241.1755972975793</v>
       </c>
       <c r="D3">
-        <v>242.5671340637374</v>
+        <v>242.7415972975793</v>
       </c>
       <c r="E3">
-        <v>-9.442</v>
+        <v>-6.984</v>
       </c>
       <c r="F3">
-        <v>2.458</v>
+        <v>4.916</v>
       </c>
       <c r="G3">
         <v>3.35</v>
@@ -1533,28 +1533,28 @@
         <v>36.448</v>
       </c>
       <c r="M3">
-        <v>0.1236374</v>
+        <v>0.2472748</v>
       </c>
       <c r="N3">
-        <v>36.3243626</v>
+        <v>36.2007252</v>
       </c>
       <c r="O3">
-        <v>5.44865439</v>
+        <v>5.43010878</v>
       </c>
       <c r="P3">
-        <v>30.87570821</v>
+        <v>30.77061642</v>
       </c>
       <c r="Q3">
-        <v>31.72770821</v>
+        <v>31.62261642</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08590078774495473</v>
+        <v>0.08624912320307264</v>
       </c>
       <c r="T3">
-        <v>0.7344600103638105</v>
+        <v>0.7408398966096</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>294.7975289030665</v>
+        <v>147.3987644515333</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08537924073901118</v>
+        <v>0.08528915161051717</v>
       </c>
       <c r="C4">
-        <v>241.1755972975793</v>
+        <v>238.8923116728427</v>
       </c>
       <c r="D4">
-        <v>242.7415972975793</v>
+        <v>242.9163116728427</v>
       </c>
       <c r="E4">
-        <v>-6.984</v>
+        <v>-4.526000000000001</v>
       </c>
       <c r="F4">
-        <v>4.916</v>
+        <v>7.374</v>
       </c>
       <c r="G4">
         <v>3.35</v>
@@ -1615,28 +1615,28 @@
         <v>36.448</v>
       </c>
       <c r="M4">
-        <v>0.2472748</v>
+        <v>0.3709122</v>
       </c>
       <c r="N4">
-        <v>36.2007252</v>
+        <v>36.0770878</v>
       </c>
       <c r="O4">
-        <v>5.43010878</v>
+        <v>5.41156317</v>
       </c>
       <c r="P4">
-        <v>30.77061642</v>
+        <v>30.66552463</v>
       </c>
       <c r="Q4">
-        <v>31.62261642</v>
+        <v>31.51752463</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08624912320307264</v>
+        <v>0.08660464083558472</v>
       </c>
       <c r="T4">
-        <v>0.7408398966096</v>
+        <v>0.7473513269016944</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>147.3987644515333</v>
+        <v>98.26584296768885</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08528915161051717</v>
+        <v>0.08519906248202318</v>
       </c>
       <c r="C5">
-        <v>238.8923116728427</v>
+        <v>236.6092777321988</v>
       </c>
       <c r="D5">
-        <v>242.9163116728427</v>
+        <v>243.0912777321988</v>
       </c>
       <c r="E5">
-        <v>-4.526000000000001</v>
+        <v>-2.068</v>
       </c>
       <c r="F5">
-        <v>7.374</v>
+        <v>9.832000000000001</v>
       </c>
       <c r="G5">
         <v>3.35</v>
@@ -1697,28 +1697,28 @@
         <v>36.448</v>
       </c>
       <c r="M5">
-        <v>0.3709122</v>
+        <v>0.4945496</v>
       </c>
       <c r="N5">
-        <v>36.0770878</v>
+        <v>35.9534504</v>
       </c>
       <c r="O5">
-        <v>5.41156317</v>
+        <v>5.39301756</v>
       </c>
       <c r="P5">
-        <v>30.66552463</v>
+        <v>30.56043284</v>
       </c>
       <c r="Q5">
-        <v>31.51752463</v>
+        <v>31.41243284</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08660464083558472</v>
+        <v>0.08696756508544082</v>
       </c>
       <c r="T5">
-        <v>0.7473513269016944</v>
+        <v>0.7539984119915408</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>98.26584296768885</v>
+        <v>73.69938222576664</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08519906248202318</v>
+        <v>0.08510897335352918</v>
       </c>
       <c r="C6">
-        <v>236.6092777321988</v>
+        <v>234.3264960198833</v>
       </c>
       <c r="D6">
-        <v>243.0912777321988</v>
+        <v>243.2664960198833</v>
       </c>
       <c r="E6">
-        <v>-2.068</v>
+        <v>0.3900000000000006</v>
       </c>
       <c r="F6">
-        <v>9.832000000000001</v>
+        <v>12.29</v>
       </c>
       <c r="G6">
         <v>3.35</v>
@@ -1779,28 +1779,28 @@
         <v>36.448</v>
       </c>
       <c r="M6">
-        <v>0.4945496</v>
+        <v>0.618187</v>
       </c>
       <c r="N6">
-        <v>35.9534504</v>
+        <v>35.829813</v>
       </c>
       <c r="O6">
-        <v>5.39301756</v>
+        <v>5.37447195</v>
       </c>
       <c r="P6">
-        <v>30.56043284</v>
+        <v>30.45534105</v>
       </c>
       <c r="Q6">
-        <v>31.41243284</v>
+        <v>31.30734105</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08696756508544082</v>
+        <v>0.08733812984582021</v>
       </c>
       <c r="T6">
-        <v>0.7539984119915408</v>
+        <v>0.7607854357148577</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>73.69938222576664</v>
+        <v>58.95950578061331</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08510897335352918</v>
+        <v>0.08501888422503519</v>
       </c>
       <c r="C7">
-        <v>234.3264960198833</v>
+        <v>232.0439670817023</v>
       </c>
       <c r="D7">
-        <v>243.2664960198833</v>
+        <v>243.4419670817023</v>
       </c>
       <c r="E7">
-        <v>0.3900000000000006</v>
+        <v>2.848000000000001</v>
       </c>
       <c r="F7">
-        <v>12.29</v>
+        <v>14.748</v>
       </c>
       <c r="G7">
         <v>3.35</v>
@@ -1861,28 +1861,28 @@
         <v>36.448</v>
       </c>
       <c r="M7">
-        <v>0.618187</v>
+        <v>0.7418244000000001</v>
       </c>
       <c r="N7">
-        <v>35.829813</v>
+        <v>35.7061756</v>
       </c>
       <c r="O7">
-        <v>5.37447195</v>
+        <v>5.35592634</v>
       </c>
       <c r="P7">
-        <v>30.45534105</v>
+        <v>30.35024926</v>
       </c>
       <c r="Q7">
-        <v>31.30734105</v>
+        <v>31.20224926</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08733812984582021</v>
+        <v>0.0877165789628034</v>
       </c>
       <c r="T7">
-        <v>0.7607854357148577</v>
+        <v>0.767716864198245</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>58.95950578061331</v>
+        <v>49.13292148384442</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08501888422503517</v>
+        <v>0.08492879509654119</v>
       </c>
       <c r="C8">
-        <v>232.0439670817023</v>
+        <v>229.7616914650378</v>
       </c>
       <c r="D8">
-        <v>243.4419670817023</v>
+        <v>243.6176914650378</v>
       </c>
       <c r="E8">
-        <v>2.847999999999999</v>
+        <v>5.305999999999999</v>
       </c>
       <c r="F8">
-        <v>14.748</v>
+        <v>17.206</v>
       </c>
       <c r="G8">
         <v>3.35</v>
@@ -1943,28 +1943,28 @@
         <v>36.448</v>
       </c>
       <c r="M8">
-        <v>0.7418243999999999</v>
+        <v>0.8654617999999999</v>
       </c>
       <c r="N8">
-        <v>35.7061756</v>
+        <v>35.5825382</v>
       </c>
       <c r="O8">
-        <v>5.35592634</v>
+        <v>5.33738073</v>
       </c>
       <c r="P8">
-        <v>30.35024926</v>
+        <v>30.24515747</v>
       </c>
       <c r="Q8">
-        <v>31.20224926</v>
+        <v>31.09715747</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0877165789628034</v>
+        <v>0.08810316677047439</v>
       </c>
       <c r="T8">
-        <v>0.767716864198245</v>
+        <v>0.7747973556597698</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>49.13292148384443</v>
+        <v>42.11393270043808</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08492879509654118</v>
+        <v>0.0848387059680472</v>
       </c>
       <c r="C9">
-        <v>229.7616914650378</v>
+        <v>227.4796697188532</v>
       </c>
       <c r="D9">
-        <v>243.6176914650378</v>
+        <v>243.7936697188532</v>
       </c>
       <c r="E9">
-        <v>5.306000000000003</v>
+        <v>7.764000000000001</v>
       </c>
       <c r="F9">
-        <v>17.206</v>
+        <v>19.664</v>
       </c>
       <c r="G9">
         <v>3.35</v>
@@ -2025,28 +2025,28 @@
         <v>36.448</v>
       </c>
       <c r="M9">
-        <v>0.8654618000000001</v>
+        <v>0.9890992000000001</v>
       </c>
       <c r="N9">
-        <v>35.5825382</v>
+        <v>35.4589008</v>
       </c>
       <c r="O9">
-        <v>5.33738073</v>
+        <v>5.31883512</v>
       </c>
       <c r="P9">
-        <v>30.24515747</v>
+        <v>30.14006568</v>
       </c>
       <c r="Q9">
-        <v>31.09715747</v>
+        <v>30.99206568</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08810316677047439</v>
+        <v>0.08849815866092087</v>
       </c>
       <c r="T9">
-        <v>0.7747973556597698</v>
+        <v>0.7820317708487191</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>42.11393270043808</v>
+        <v>36.84969111288332</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0848387059680472</v>
+        <v>0.0847486168395532</v>
       </c>
       <c r="C10">
-        <v>227.4796697188532</v>
+        <v>225.1979023936995</v>
       </c>
       <c r="D10">
-        <v>243.7936697188532</v>
+        <v>243.9699023936995</v>
       </c>
       <c r="E10">
-        <v>7.764000000000001</v>
+        <v>10.222</v>
       </c>
       <c r="F10">
-        <v>19.664</v>
+        <v>22.122</v>
       </c>
       <c r="G10">
         <v>3.35</v>
@@ -2107,28 +2107,28 @@
         <v>36.448</v>
       </c>
       <c r="M10">
-        <v>0.9890992000000001</v>
+        <v>1.1127366</v>
       </c>
       <c r="N10">
-        <v>35.4589008</v>
+        <v>35.3352634</v>
       </c>
       <c r="O10">
-        <v>5.31883512</v>
+        <v>5.30028951</v>
       </c>
       <c r="P10">
-        <v>30.14006568</v>
+        <v>30.03497389</v>
       </c>
       <c r="Q10">
-        <v>30.99206568</v>
+        <v>30.88697389</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08849815866092087</v>
+        <v>0.0889018316918167</v>
       </c>
       <c r="T10">
-        <v>0.7820317708487191</v>
+        <v>0.7894251841736891</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>36.84969111288332</v>
+        <v>32.75528098922962</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0847486168395532</v>
+        <v>0.08465852771105921</v>
       </c>
       <c r="C11">
-        <v>225.1979023936995</v>
+        <v>222.9163900417206</v>
       </c>
       <c r="D11">
-        <v>243.9699023936995</v>
+        <v>244.1463900417206</v>
       </c>
       <c r="E11">
-        <v>10.222</v>
+        <v>12.68</v>
       </c>
       <c r="F11">
-        <v>22.122</v>
+        <v>24.58</v>
       </c>
       <c r="G11">
         <v>3.35</v>
@@ -2189,28 +2189,28 @@
         <v>36.448</v>
       </c>
       <c r="M11">
-        <v>1.1127366</v>
+        <v>1.236374</v>
       </c>
       <c r="N11">
-        <v>35.3352634</v>
+        <v>35.211626</v>
       </c>
       <c r="O11">
-        <v>5.30028951</v>
+        <v>5.2817439</v>
       </c>
       <c r="P11">
-        <v>30.03497389</v>
+        <v>29.9298821</v>
       </c>
       <c r="Q11">
-        <v>30.88697389</v>
+        <v>30.7818821</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0889018316918167</v>
+        <v>0.08931447523451022</v>
       </c>
       <c r="T11">
-        <v>0.7894251841736891</v>
+        <v>0.7969828955725475</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>32.75528098922962</v>
+        <v>29.47975289030666</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08465852771105921</v>
+        <v>0.0845684385825652</v>
       </c>
       <c r="C12">
-        <v>222.9163900417206</v>
+        <v>220.6351332166594</v>
       </c>
       <c r="D12">
-        <v>244.1463900417206</v>
+        <v>244.3231332166594</v>
       </c>
       <c r="E12">
-        <v>12.68</v>
+        <v>15.138</v>
       </c>
       <c r="F12">
-        <v>24.58</v>
+        <v>27.038</v>
       </c>
       <c r="G12">
         <v>3.35</v>
@@ -2271,28 +2271,28 @@
         <v>36.448</v>
       </c>
       <c r="M12">
-        <v>1.236374</v>
+        <v>1.3600114</v>
       </c>
       <c r="N12">
-        <v>35.211626</v>
+        <v>35.0879886</v>
       </c>
       <c r="O12">
-        <v>5.2817439</v>
+        <v>5.26319829</v>
       </c>
       <c r="P12">
-        <v>29.9298821</v>
+        <v>29.82479031</v>
       </c>
       <c r="Q12">
-        <v>30.7818821</v>
+        <v>30.67679031</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08931447523451022</v>
+        <v>0.08973639166580359</v>
       </c>
       <c r="T12">
-        <v>0.7969828955725475</v>
+        <v>0.8047104431826161</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>29.47975289030666</v>
+        <v>26.79977535482423</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0845684385825652</v>
+        <v>0.08447834945407121</v>
       </c>
       <c r="C13">
-        <v>220.6351332166594</v>
+        <v>218.3541324738632</v>
       </c>
       <c r="D13">
-        <v>244.3231332166594</v>
+        <v>244.5001324738632</v>
       </c>
       <c r="E13">
-        <v>15.138</v>
+        <v>17.596</v>
       </c>
       <c r="F13">
-        <v>27.038</v>
+        <v>29.496</v>
       </c>
       <c r="G13">
         <v>3.35</v>
@@ -2353,28 +2353,28 @@
         <v>36.448</v>
       </c>
       <c r="M13">
-        <v>1.3600114</v>
+        <v>1.4836488</v>
       </c>
       <c r="N13">
-        <v>35.0879886</v>
+        <v>34.9643512</v>
       </c>
       <c r="O13">
-        <v>5.26319829</v>
+        <v>5.244652680000001</v>
       </c>
       <c r="P13">
-        <v>29.82479031</v>
+        <v>29.71969852</v>
       </c>
       <c r="Q13">
-        <v>30.67679031</v>
+        <v>30.57169852</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08973639166580359</v>
+        <v>0.0901678971068991</v>
       </c>
       <c r="T13">
-        <v>0.8047104431826161</v>
+        <v>0.8126136168747318</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>26.79977535482423</v>
+        <v>24.56646074192222</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08447834945407121</v>
+        <v>0.0843882603255772</v>
       </c>
       <c r="C14">
-        <v>218.3541324738632</v>
+        <v>216.0733883702899</v>
       </c>
       <c r="D14">
-        <v>244.5001324738632</v>
+        <v>244.6773883702899</v>
       </c>
       <c r="E14">
-        <v>17.596</v>
+        <v>20.054</v>
       </c>
       <c r="F14">
-        <v>29.496</v>
+        <v>31.954</v>
       </c>
       <c r="G14">
         <v>3.35</v>
@@ -2435,28 +2435,28 @@
         <v>36.448</v>
       </c>
       <c r="M14">
-        <v>1.4836488</v>
+        <v>1.6072862</v>
       </c>
       <c r="N14">
-        <v>34.9643512</v>
+        <v>34.8407138</v>
       </c>
       <c r="O14">
-        <v>5.244652680000001</v>
+        <v>5.22610707</v>
       </c>
       <c r="P14">
-        <v>29.71969852</v>
+        <v>29.61460673</v>
       </c>
       <c r="Q14">
-        <v>30.57169852</v>
+        <v>30.46660673</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0901678971068991</v>
+        <v>0.09060932221330713</v>
       </c>
       <c r="T14">
-        <v>0.8126136168747318</v>
+        <v>0.8206984727206891</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>24.56646074192222</v>
+        <v>22.67673299254358</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0843882603255772</v>
+        <v>0.0842981711970832</v>
       </c>
       <c r="C15">
-        <v>216.0733883702899</v>
+        <v>213.7929014645138</v>
       </c>
       <c r="D15">
-        <v>244.6773883702899</v>
+        <v>244.8549014645138</v>
       </c>
       <c r="E15">
-        <v>20.054</v>
+        <v>22.51200000000001</v>
       </c>
       <c r="F15">
-        <v>31.954</v>
+        <v>34.41200000000001</v>
       </c>
       <c r="G15">
         <v>3.35</v>
@@ -2517,28 +2517,28 @@
         <v>36.448</v>
       </c>
       <c r="M15">
-        <v>1.6072862</v>
+        <v>1.7309236</v>
       </c>
       <c r="N15">
-        <v>34.8407138</v>
+        <v>34.7170764</v>
       </c>
       <c r="O15">
-        <v>5.22610707</v>
+        <v>5.20756146</v>
       </c>
       <c r="P15">
-        <v>29.61460673</v>
+        <v>29.50951494</v>
       </c>
       <c r="Q15">
-        <v>30.46660673</v>
+        <v>30.36151494</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09060932221330713</v>
+        <v>0.09106101301986419</v>
       </c>
       <c r="T15">
-        <v>0.8206984727206891</v>
+        <v>0.8289713484700407</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>22.67673299254358</v>
+        <v>21.05696635021904</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0842981711970832</v>
+        <v>0.08420808206858921</v>
       </c>
       <c r="C16">
-        <v>213.7929014645138</v>
+        <v>211.512672316731</v>
       </c>
       <c r="D16">
-        <v>244.8549014645138</v>
+        <v>245.032672316731</v>
       </c>
       <c r="E16">
-        <v>22.51200000000001</v>
+        <v>24.97000000000001</v>
       </c>
       <c r="F16">
-        <v>34.41200000000001</v>
+        <v>36.87</v>
       </c>
       <c r="G16">
         <v>3.35</v>
@@ -2599,28 +2599,28 @@
         <v>36.448</v>
       </c>
       <c r="M16">
-        <v>1.7309236</v>
+        <v>1.854561</v>
       </c>
       <c r="N16">
-        <v>34.7170764</v>
+        <v>34.593439</v>
       </c>
       <c r="O16">
-        <v>5.20756146</v>
+        <v>5.189015850000001</v>
       </c>
       <c r="P16">
-        <v>29.50951494</v>
+        <v>29.40442315</v>
       </c>
       <c r="Q16">
-        <v>30.36151494</v>
+        <v>30.25642315</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09106101301986419</v>
+        <v>0.09152333184539907</v>
       </c>
       <c r="T16">
-        <v>0.8289713484700407</v>
+        <v>0.8374388801193773</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>21.05696635021904</v>
+        <v>19.65316859353777</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08420808206858921</v>
+        <v>0.0841179929400952</v>
       </c>
       <c r="C17">
-        <v>211.512672316731</v>
+        <v>209.2327014887661</v>
       </c>
       <c r="D17">
-        <v>245.032672316731</v>
+        <v>245.2107014887661</v>
       </c>
       <c r="E17">
-        <v>24.97</v>
+        <v>27.428</v>
       </c>
       <c r="F17">
-        <v>36.87</v>
+        <v>39.328</v>
       </c>
       <c r="G17">
         <v>3.35</v>
@@ -2681,28 +2681,28 @@
         <v>36.448</v>
       </c>
       <c r="M17">
-        <v>1.854561</v>
+        <v>1.9781984</v>
       </c>
       <c r="N17">
-        <v>34.593439</v>
+        <v>34.4698016</v>
       </c>
       <c r="O17">
-        <v>5.189015850000001</v>
+        <v>5.170470239999999</v>
       </c>
       <c r="P17">
-        <v>29.40442315</v>
+        <v>29.29933136</v>
       </c>
       <c r="Q17">
-        <v>30.25642315</v>
+        <v>30.15133136</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09152333184539907</v>
+        <v>0.09199665826201811</v>
       </c>
       <c r="T17">
-        <v>0.8374388801193773</v>
+        <v>0.8461080196651266</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>19.65316859353777</v>
+        <v>18.42484555644166</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0841179929400952</v>
+        <v>0.08402790381160122</v>
       </c>
       <c r="C18">
-        <v>209.2327014887661</v>
+        <v>206.9529895440773</v>
       </c>
       <c r="D18">
-        <v>245.2107014887661</v>
+        <v>245.3889895440773</v>
       </c>
       <c r="E18">
-        <v>27.428</v>
+        <v>29.88600000000001</v>
       </c>
       <c r="F18">
-        <v>39.328</v>
+        <v>41.78600000000001</v>
       </c>
       <c r="G18">
         <v>3.35</v>
@@ -2763,28 +2763,28 @@
         <v>36.448</v>
       </c>
       <c r="M18">
-        <v>1.9781984</v>
+        <v>2.1018358</v>
       </c>
       <c r="N18">
-        <v>34.4698016</v>
+        <v>34.3461642</v>
       </c>
       <c r="O18">
-        <v>5.170470239999999</v>
+        <v>5.151924629999999</v>
       </c>
       <c r="P18">
-        <v>29.29933136</v>
+        <v>29.19423957</v>
       </c>
       <c r="Q18">
-        <v>30.15133136</v>
+        <v>30.04623957</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09199665826201811</v>
+        <v>0.09248139013445929</v>
       </c>
       <c r="T18">
-        <v>0.8461080196651266</v>
+        <v>0.8549860541396891</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>18.42484555644166</v>
+        <v>17.34103111194509</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08402790381160122</v>
+        <v>0.08393781468310721</v>
       </c>
       <c r="C19">
-        <v>206.9529895440773</v>
+        <v>204.6735370477628</v>
       </c>
       <c r="D19">
-        <v>245.3889895440773</v>
+        <v>245.5675370477628</v>
       </c>
       <c r="E19">
-        <v>29.88600000000001</v>
+        <v>32.34400000000001</v>
       </c>
       <c r="F19">
-        <v>41.78600000000001</v>
+        <v>44.24400000000001</v>
       </c>
       <c r="G19">
         <v>3.35</v>
@@ -2845,28 +2845,28 @@
         <v>36.448</v>
       </c>
       <c r="M19">
-        <v>2.1018358</v>
+        <v>2.2254732</v>
       </c>
       <c r="N19">
-        <v>34.3461642</v>
+        <v>34.2225268</v>
       </c>
       <c r="O19">
-        <v>5.151924629999999</v>
+        <v>5.13337902</v>
       </c>
       <c r="P19">
-        <v>29.19423957</v>
+        <v>29.08914778</v>
       </c>
       <c r="Q19">
-        <v>30.04623957</v>
+        <v>29.94114778</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09248139013445929</v>
+        <v>0.09297794473549659</v>
       </c>
       <c r="T19">
-        <v>0.8549860541396891</v>
+        <v>0.8640806260404603</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>17.34103111194509</v>
+        <v>16.37764049461481</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08393781468310721</v>
+        <v>0.08384772555461321</v>
       </c>
       <c r="C20">
-        <v>204.6735370477628</v>
+        <v>202.3943445665669</v>
       </c>
       <c r="D20">
-        <v>245.5675370477628</v>
+        <v>245.7463445665669</v>
       </c>
       <c r="E20">
-        <v>32.344</v>
+        <v>34.80200000000001</v>
       </c>
       <c r="F20">
-        <v>44.244</v>
+        <v>46.70200000000001</v>
       </c>
       <c r="G20">
         <v>3.35</v>
@@ -2927,28 +2927,28 @@
         <v>36.448</v>
       </c>
       <c r="M20">
-        <v>2.2254732</v>
+        <v>2.3491106</v>
       </c>
       <c r="N20">
-        <v>34.2225268</v>
+        <v>34.0988894</v>
       </c>
       <c r="O20">
-        <v>5.13337902</v>
+        <v>5.114833409999999</v>
       </c>
       <c r="P20">
-        <v>29.08914778</v>
+        <v>28.98405599</v>
       </c>
       <c r="Q20">
-        <v>29.94114778</v>
+        <v>29.83605599</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09297794473549659</v>
+        <v>0.09348675994396692</v>
       </c>
       <c r="T20">
-        <v>0.8640806260404603</v>
+        <v>0.8733997552721149</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>16.37764049461481</v>
+        <v>15.51565941595087</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08384772555461321</v>
+        <v>0.08375763642611921</v>
       </c>
       <c r="C21">
-        <v>202.3943445665669</v>
+        <v>200.1154126688855</v>
       </c>
       <c r="D21">
-        <v>245.7463445665669</v>
+        <v>245.9254126688855</v>
       </c>
       <c r="E21">
-        <v>34.80200000000001</v>
+        <v>37.26000000000001</v>
       </c>
       <c r="F21">
-        <v>46.70200000000001</v>
+        <v>49.16</v>
       </c>
       <c r="G21">
         <v>3.35</v>
@@ -3009,28 +3009,28 @@
         <v>36.448</v>
       </c>
       <c r="M21">
-        <v>2.3491106</v>
+        <v>2.472748</v>
       </c>
       <c r="N21">
-        <v>34.0988894</v>
+        <v>33.975252</v>
       </c>
       <c r="O21">
-        <v>5.114833409999999</v>
+        <v>5.0962878</v>
       </c>
       <c r="P21">
-        <v>28.98405599</v>
+        <v>28.8789642</v>
       </c>
       <c r="Q21">
-        <v>29.83605599</v>
+        <v>29.7309642</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09348675994396692</v>
+        <v>0.094008295532649</v>
       </c>
       <c r="T21">
-        <v>0.8733997552721149</v>
+        <v>0.8829518627345608</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>15.51565941595087</v>
+        <v>14.73987644515332</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08375763642611921</v>
+        <v>0.08366754729762521</v>
       </c>
       <c r="C22">
-        <v>200.1154126688855</v>
+        <v>197.8367419247724</v>
       </c>
       <c r="D22">
-        <v>245.9254126688855</v>
+        <v>246.1047419247724</v>
       </c>
       <c r="E22">
-        <v>37.26000000000001</v>
+        <v>39.71800000000001</v>
       </c>
       <c r="F22">
-        <v>49.16</v>
+        <v>51.61800000000001</v>
       </c>
       <c r="G22">
         <v>3.35</v>
@@ -3091,28 +3091,28 @@
         <v>36.448</v>
       </c>
       <c r="M22">
-        <v>2.472748</v>
+        <v>2.5963854</v>
       </c>
       <c r="N22">
-        <v>33.975252</v>
+        <v>33.8516146</v>
       </c>
       <c r="O22">
-        <v>5.0962878</v>
+        <v>5.077742189999999</v>
       </c>
       <c r="P22">
-        <v>28.8789642</v>
+        <v>28.77387241</v>
       </c>
       <c r="Q22">
-        <v>29.7309642</v>
+        <v>29.62587241</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.094008295532649</v>
+        <v>0.09454303455395596</v>
       </c>
       <c r="T22">
-        <v>0.8829518627345608</v>
+        <v>0.8927457957023852</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>14.73987644515332</v>
+        <v>14.03797756681269</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08366754729762521</v>
+        <v>0.08357745816913122</v>
       </c>
       <c r="C23">
-        <v>197.8367419247724</v>
+        <v>195.5583329059456</v>
       </c>
       <c r="D23">
-        <v>246.1047419247724</v>
+        <v>246.2843329059456</v>
       </c>
       <c r="E23">
-        <v>39.718</v>
+        <v>42.176</v>
       </c>
       <c r="F23">
-        <v>51.618</v>
+        <v>54.076</v>
       </c>
       <c r="G23">
         <v>3.35</v>
@@ -3173,28 +3173,28 @@
         <v>36.448</v>
       </c>
       <c r="M23">
-        <v>2.5963854</v>
+        <v>2.7200228</v>
       </c>
       <c r="N23">
-        <v>33.8516146</v>
+        <v>33.7279772</v>
       </c>
       <c r="O23">
-        <v>5.077742189999999</v>
+        <v>5.059196579999999</v>
       </c>
       <c r="P23">
-        <v>28.77387241</v>
+        <v>28.66878062</v>
       </c>
       <c r="Q23">
-        <v>29.62587241</v>
+        <v>29.52078062</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09454303455395596</v>
+        <v>0.09509148483221951</v>
       </c>
       <c r="T23">
-        <v>0.8927457957023851</v>
+        <v>0.902790855156564</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>14.03797756681269</v>
+        <v>13.39988767741212</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08357745816913122</v>
+        <v>0.08378061904063722</v>
       </c>
       <c r="C24">
-        <v>195.5583329059456</v>
+        <v>192.6957058604675</v>
       </c>
       <c r="D24">
-        <v>246.2843329059456</v>
+        <v>245.8797058604675</v>
       </c>
       <c r="E24">
-        <v>42.176</v>
+        <v>44.63400000000001</v>
       </c>
       <c r="F24">
-        <v>54.076</v>
+        <v>56.53400000000001</v>
       </c>
       <c r="G24">
         <v>3.35</v>
@@ -3255,45 +3255,45 @@
         <v>36.448</v>
       </c>
       <c r="M24">
-        <v>2.7200228</v>
+        <v>2.9284612</v>
       </c>
       <c r="N24">
-        <v>33.7279772</v>
+        <v>33.5195388</v>
       </c>
       <c r="O24">
-        <v>5.059196579999999</v>
+        <v>5.02793082</v>
       </c>
       <c r="P24">
-        <v>28.66878062</v>
+        <v>28.49160798</v>
       </c>
       <c r="Q24">
-        <v>29.52078062</v>
+        <v>29.34360798</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09509148483221951</v>
+        <v>0.09565418057225611</v>
       </c>
       <c r="T24">
-        <v>0.902790855156564</v>
+        <v>0.9130968252459162</v>
       </c>
       <c r="U24">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V24">
         <v>0.15</v>
       </c>
       <c r="W24">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y24">
-        <v>13.39988767741212</v>
+        <v>12.44612699666296</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08378061904063722</v>
+        <v>0.08370327991214321</v>
       </c>
       <c r="C25">
-        <v>192.6957058604675</v>
+        <v>190.3915821547229</v>
       </c>
       <c r="D25">
-        <v>245.8797058604675</v>
+        <v>246.0335821547229</v>
       </c>
       <c r="E25">
-        <v>44.63400000000001</v>
+        <v>47.09200000000001</v>
       </c>
       <c r="F25">
-        <v>56.53400000000001</v>
+        <v>58.992</v>
       </c>
       <c r="G25">
         <v>3.35</v>
@@ -3337,28 +3337,28 @@
         <v>36.448</v>
       </c>
       <c r="M25">
-        <v>2.9284612</v>
+        <v>3.0557856</v>
       </c>
       <c r="N25">
-        <v>33.5195388</v>
+        <v>33.3922144</v>
       </c>
       <c r="O25">
-        <v>5.02793082</v>
+        <v>5.00883216</v>
       </c>
       <c r="P25">
-        <v>28.49160798</v>
+        <v>28.38338224</v>
       </c>
       <c r="Q25">
-        <v>29.34360798</v>
+        <v>29.23538224</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09565418057225611</v>
+        <v>0.09623168409492527</v>
       </c>
       <c r="T25">
-        <v>0.9130968252459162</v>
+        <v>0.923674005074462</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>12.44612699666296</v>
+        <v>11.927538371802</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08370327991214321</v>
+        <v>0.08362594078364921</v>
       </c>
       <c r="C26">
-        <v>190.3915821547229</v>
+        <v>188.0876511671307</v>
       </c>
       <c r="D26">
-        <v>246.0335821547229</v>
+        <v>246.1876511671307</v>
       </c>
       <c r="E26">
-        <v>47.092</v>
+        <v>49.55</v>
       </c>
       <c r="F26">
-        <v>58.992</v>
+        <v>61.45</v>
       </c>
       <c r="G26">
         <v>3.35</v>
@@ -3419,28 +3419,28 @@
         <v>36.448</v>
       </c>
       <c r="M26">
-        <v>3.0557856</v>
+        <v>3.18311</v>
       </c>
       <c r="N26">
-        <v>33.3922144</v>
+        <v>33.26489</v>
       </c>
       <c r="O26">
-        <v>5.00883216</v>
+        <v>4.9897335</v>
       </c>
       <c r="P26">
-        <v>28.38338224</v>
+        <v>28.2751565</v>
       </c>
       <c r="Q26">
-        <v>29.23538224</v>
+        <v>29.1271565</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09623168409492527</v>
+        <v>0.09682458771153228</v>
       </c>
       <c r="T26">
-        <v>0.923674005074462</v>
+        <v>0.9345332430317688</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.927538371802</v>
+        <v>11.45043683692992</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08362594078364921</v>
+        <v>0.08354860165515521</v>
       </c>
       <c r="C27">
-        <v>188.0876511671307</v>
+        <v>185.7839132599646</v>
       </c>
       <c r="D27">
-        <v>246.1876511671307</v>
+        <v>246.3419132599646</v>
       </c>
       <c r="E27">
-        <v>49.55</v>
+        <v>52.00800000000001</v>
       </c>
       <c r="F27">
-        <v>61.45</v>
+        <v>63.90800000000001</v>
       </c>
       <c r="G27">
         <v>3.35</v>
@@ -3501,28 +3501,28 @@
         <v>36.448</v>
       </c>
       <c r="M27">
-        <v>3.18311</v>
+        <v>3.310434400000001</v>
       </c>
       <c r="N27">
-        <v>33.26489</v>
+        <v>33.1375656</v>
       </c>
       <c r="O27">
-        <v>4.9897335</v>
+        <v>4.97063484</v>
       </c>
       <c r="P27">
-        <v>28.2751565</v>
+        <v>28.16693076</v>
       </c>
       <c r="Q27">
-        <v>29.1271565</v>
+        <v>29.01893076</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09682458771153228</v>
+        <v>0.09743351575020975</v>
       </c>
       <c r="T27">
-        <v>0.9345332430317688</v>
+        <v>0.9456859739068408</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.45043683692992</v>
+        <v>11.01003542012492</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08354860165515521</v>
+        <v>0.08347126252666122</v>
       </c>
       <c r="C28">
-        <v>185.7839132599646</v>
+        <v>183.4803687964069</v>
       </c>
       <c r="D28">
-        <v>246.3419132599646</v>
+        <v>246.4963687964069</v>
       </c>
       <c r="E28">
-        <v>52.00800000000001</v>
+        <v>54.46600000000002</v>
       </c>
       <c r="F28">
-        <v>63.90800000000001</v>
+        <v>66.36600000000001</v>
       </c>
       <c r="G28">
         <v>3.35</v>
@@ -3583,28 +3583,28 @@
         <v>36.448</v>
       </c>
       <c r="M28">
-        <v>3.310434400000001</v>
+        <v>3.437758800000001</v>
       </c>
       <c r="N28">
-        <v>33.1375656</v>
+        <v>33.0102412</v>
       </c>
       <c r="O28">
-        <v>4.97063484</v>
+        <v>4.951536180000001</v>
       </c>
       <c r="P28">
-        <v>28.16693076</v>
+        <v>28.05870502</v>
       </c>
       <c r="Q28">
-        <v>29.01893076</v>
+        <v>28.91070502</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09743351575020975</v>
+        <v>0.09805912674885099</v>
       </c>
       <c r="T28">
-        <v>0.9456859739068408</v>
+        <v>0.9571442590524629</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.01003542012492</v>
+        <v>10.60225633049067</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08347126252666122</v>
+        <v>0.08339392339816722</v>
       </c>
       <c r="C29">
-        <v>183.4803687964069</v>
+        <v>181.1770181405514</v>
       </c>
       <c r="D29">
-        <v>246.4963687964069</v>
+        <v>246.6510181405514</v>
       </c>
       <c r="E29">
-        <v>54.46600000000002</v>
+        <v>56.92400000000001</v>
       </c>
       <c r="F29">
-        <v>66.36600000000001</v>
+        <v>68.82400000000001</v>
       </c>
       <c r="G29">
         <v>3.35</v>
@@ -3665,28 +3665,28 @@
         <v>36.448</v>
       </c>
       <c r="M29">
-        <v>3.437758800000001</v>
+        <v>3.565083200000001</v>
       </c>
       <c r="N29">
-        <v>33.0102412</v>
+        <v>32.8829168</v>
       </c>
       <c r="O29">
-        <v>4.951536180000001</v>
+        <v>4.93243752</v>
       </c>
       <c r="P29">
-        <v>28.05870502</v>
+        <v>27.95047928</v>
       </c>
       <c r="Q29">
-        <v>28.91070502</v>
+        <v>28.80247928</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09805912674885099</v>
+        <v>0.09870211583078781</v>
       </c>
       <c r="T29">
-        <v>0.9571442590524629</v>
+        <v>0.9689208298965744</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.60225633049067</v>
+        <v>10.22360431868743</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08339392339816722</v>
+        <v>0.08331658426967323</v>
       </c>
       <c r="C30">
-        <v>181.1770181405514</v>
+        <v>178.8738616574059</v>
       </c>
       <c r="D30">
-        <v>246.6510181405514</v>
+        <v>246.805861657406</v>
       </c>
       <c r="E30">
-        <v>56.92400000000001</v>
+        <v>59.38200000000001</v>
       </c>
       <c r="F30">
-        <v>68.82400000000001</v>
+        <v>71.28200000000001</v>
       </c>
       <c r="G30">
         <v>3.35</v>
@@ -3747,28 +3747,28 @@
         <v>36.448</v>
       </c>
       <c r="M30">
-        <v>3.565083200000001</v>
+        <v>3.692407600000001</v>
       </c>
       <c r="N30">
-        <v>32.8829168</v>
+        <v>32.7555924</v>
       </c>
       <c r="O30">
-        <v>4.93243752</v>
+        <v>4.91333886</v>
       </c>
       <c r="P30">
-        <v>27.95047928</v>
+        <v>27.84225354</v>
       </c>
       <c r="Q30">
-        <v>28.80247928</v>
+        <v>28.69425354</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09870211583078781</v>
+        <v>0.09936321728122989</v>
       </c>
       <c r="T30">
-        <v>0.9689208298965744</v>
+        <v>0.9810291351306607</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.22360431868743</v>
+        <v>9.871066238732688</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08331658426967321</v>
+        <v>0.08367274514117923</v>
       </c>
       <c r="C31">
-        <v>178.873861657406</v>
+        <v>175.7043881129854</v>
       </c>
       <c r="D31">
-        <v>246.805861657406</v>
+        <v>246.0943881129854</v>
       </c>
       <c r="E31">
-        <v>59.382</v>
+        <v>61.84</v>
       </c>
       <c r="F31">
-        <v>71.282</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="G31">
         <v>3.35</v>
@@ -3829,45 +3829,45 @@
         <v>36.448</v>
       </c>
       <c r="M31">
-        <v>3.6924076</v>
+        <v>3.94509</v>
       </c>
       <c r="N31">
-        <v>32.7555924</v>
+        <v>32.50291</v>
       </c>
       <c r="O31">
-        <v>4.91333886</v>
+        <v>4.8754365</v>
       </c>
       <c r="P31">
-        <v>27.84225354</v>
+        <v>27.6274735</v>
       </c>
       <c r="Q31">
-        <v>28.69425354</v>
+        <v>28.4794735</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09936321728122989</v>
+        <v>0.1000432073445418</v>
       </c>
       <c r="T31">
-        <v>0.9810291351306607</v>
+        <v>0.9934833919428638</v>
       </c>
       <c r="U31">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V31">
         <v>0.15</v>
       </c>
       <c r="W31">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>9.871066238732691</v>
+        <v>9.23882598369112</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08367274514117923</v>
+        <v>0.08360985601268522</v>
       </c>
       <c r="C32">
-        <v>175.7043881129854</v>
+        <v>173.3717182420363</v>
       </c>
       <c r="D32">
-        <v>246.0943881129854</v>
+        <v>246.2197182420363</v>
       </c>
       <c r="E32">
-        <v>61.84</v>
+        <v>64.298</v>
       </c>
       <c r="F32">
-        <v>73.73999999999999</v>
+        <v>76.19800000000001</v>
       </c>
       <c r="G32">
         <v>3.35</v>
@@ -3911,28 +3911,28 @@
         <v>36.448</v>
       </c>
       <c r="M32">
-        <v>3.94509</v>
+        <v>4.076593</v>
       </c>
       <c r="N32">
-        <v>32.50291</v>
+        <v>32.371407</v>
       </c>
       <c r="O32">
-        <v>4.8754365</v>
+        <v>4.855711049999999</v>
       </c>
       <c r="P32">
-        <v>27.6274735</v>
+        <v>27.51569595</v>
       </c>
       <c r="Q32">
-        <v>28.4794735</v>
+        <v>28.36769595</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1000432073445418</v>
+        <v>0.1007429072647612</v>
       </c>
       <c r="T32">
-        <v>0.9934833919428638</v>
+        <v>1.006298641706145</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>9.23882598369112</v>
+        <v>8.940799339055921</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08360985601268522</v>
+        <v>0.08354696688419121</v>
       </c>
       <c r="C33">
-        <v>173.3717182420363</v>
+        <v>171.0391760915524</v>
       </c>
       <c r="D33">
-        <v>246.2197182420363</v>
+        <v>246.3451760915524</v>
       </c>
       <c r="E33">
-        <v>64.298</v>
+        <v>66.756</v>
       </c>
       <c r="F33">
-        <v>76.19800000000001</v>
+        <v>78.65600000000001</v>
       </c>
       <c r="G33">
         <v>3.35</v>
@@ -3993,28 +3993,28 @@
         <v>36.448</v>
       </c>
       <c r="M33">
-        <v>4.076593</v>
+        <v>4.208096</v>
       </c>
       <c r="N33">
-        <v>32.371407</v>
+        <v>32.239904</v>
       </c>
       <c r="O33">
-        <v>4.855711049999999</v>
+        <v>4.8359856</v>
       </c>
       <c r="P33">
-        <v>27.51569595</v>
+        <v>27.4039184</v>
       </c>
       <c r="Q33">
-        <v>28.36769595</v>
+        <v>28.2559184</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1007429072647612</v>
+        <v>0.1014631865943988</v>
       </c>
       <c r="T33">
-        <v>1.006298641706145</v>
+        <v>1.019490810580111</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.940799339055921</v>
+        <v>8.661399359710426</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08354696688419121</v>
+        <v>0.08348407775569722</v>
       </c>
       <c r="C34">
-        <v>171.0391760915524</v>
+        <v>168.7067618568678</v>
       </c>
       <c r="D34">
-        <v>246.3451760915524</v>
+        <v>246.4707618568678</v>
       </c>
       <c r="E34">
-        <v>66.756</v>
+        <v>69.214</v>
       </c>
       <c r="F34">
-        <v>78.65600000000001</v>
+        <v>81.114</v>
       </c>
       <c r="G34">
         <v>3.35</v>
@@ -4075,28 +4075,28 @@
         <v>36.448</v>
       </c>
       <c r="M34">
-        <v>4.208096</v>
+        <v>4.339599</v>
       </c>
       <c r="N34">
-        <v>32.239904</v>
+        <v>32.108401</v>
       </c>
       <c r="O34">
-        <v>4.8359856</v>
+        <v>4.81626015</v>
       </c>
       <c r="P34">
-        <v>27.4039184</v>
+        <v>27.29214085</v>
       </c>
       <c r="Q34">
-        <v>28.2559184</v>
+        <v>28.14414085</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1014631865943988</v>
+        <v>0.1022049667995481</v>
       </c>
       <c r="T34">
-        <v>1.019490810580111</v>
+        <v>1.033076775539868</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.661399359710426</v>
+        <v>8.398932712446474</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08348407775569722</v>
+        <v>0.08342118862720323</v>
       </c>
       <c r="C35">
-        <v>168.7067618568678</v>
+        <v>166.374475733715</v>
       </c>
       <c r="D35">
-        <v>246.4707618568678</v>
+        <v>246.596475733715</v>
       </c>
       <c r="E35">
-        <v>69.214</v>
+        <v>71.67200000000001</v>
       </c>
       <c r="F35">
-        <v>81.114</v>
+        <v>83.57200000000002</v>
       </c>
       <c r="G35">
         <v>3.35</v>
@@ -4157,28 +4157,28 @@
         <v>36.448</v>
       </c>
       <c r="M35">
-        <v>4.339599</v>
+        <v>4.471102000000001</v>
       </c>
       <c r="N35">
-        <v>32.108401</v>
+        <v>31.976898</v>
       </c>
       <c r="O35">
-        <v>4.81626015</v>
+        <v>4.7965347</v>
       </c>
       <c r="P35">
-        <v>27.29214085</v>
+        <v>27.1803633</v>
       </c>
       <c r="Q35">
-        <v>28.14414085</v>
+        <v>28.0323633</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1022049667995481</v>
+        <v>0.1029692251927322</v>
       </c>
       <c r="T35">
-        <v>1.033076775539868</v>
+        <v>1.047074436407496</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.398932712446474</v>
+        <v>8.151905279727456</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08342118862720323</v>
+        <v>0.08335829949870921</v>
       </c>
       <c r="C36">
-        <v>166.374475733715</v>
+        <v>164.0423179182263</v>
       </c>
       <c r="D36">
-        <v>246.596475733715</v>
+        <v>246.7223179182263</v>
       </c>
       <c r="E36">
-        <v>71.67200000000001</v>
+        <v>74.13000000000001</v>
       </c>
       <c r="F36">
-        <v>83.57200000000002</v>
+        <v>86.03000000000002</v>
       </c>
       <c r="G36">
         <v>3.35</v>
@@ -4239,28 +4239,28 @@
         <v>36.448</v>
       </c>
       <c r="M36">
-        <v>4.471102000000001</v>
+        <v>4.602605000000001</v>
       </c>
       <c r="N36">
-        <v>31.976898</v>
+        <v>31.845395</v>
       </c>
       <c r="O36">
-        <v>4.7965347</v>
+        <v>4.776809249999999</v>
       </c>
       <c r="P36">
-        <v>27.1803633</v>
+        <v>27.06858575</v>
       </c>
       <c r="Q36">
-        <v>28.0323633</v>
+        <v>27.92058575</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1029692251927322</v>
+        <v>0.1037569992287834</v>
       </c>
       <c r="T36">
-        <v>1.047074436407496</v>
+        <v>1.061502794532589</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.151905279727456</v>
+        <v>7.918993700306673</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08335829949870921</v>
+        <v>0.08329541037021521</v>
       </c>
       <c r="C37">
-        <v>164.0423179182263</v>
+        <v>161.7102886069345</v>
       </c>
       <c r="D37">
-        <v>246.7223179182263</v>
+        <v>246.8482886069345</v>
       </c>
       <c r="E37">
-        <v>74.13000000000001</v>
+        <v>76.58800000000001</v>
       </c>
       <c r="F37">
-        <v>86.03000000000002</v>
+        <v>88.48800000000001</v>
       </c>
       <c r="G37">
         <v>3.35</v>
@@ -4321,28 +4321,28 @@
         <v>36.448</v>
       </c>
       <c r="M37">
-        <v>4.602605000000001</v>
+        <v>4.734108000000001</v>
       </c>
       <c r="N37">
-        <v>31.845395</v>
+        <v>31.713892</v>
       </c>
       <c r="O37">
-        <v>4.776809249999999</v>
+        <v>4.7570838</v>
       </c>
       <c r="P37">
-        <v>27.06858575</v>
+        <v>26.9568082</v>
       </c>
       <c r="Q37">
-        <v>27.92058575</v>
+        <v>27.8088082</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1037569992287834</v>
+        <v>0.1045693912034613</v>
       </c>
       <c r="T37">
-        <v>1.061502794532589</v>
+        <v>1.076382038849091</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.918993700306673</v>
+        <v>7.699021653075932</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08329541037021522</v>
+        <v>0.08348412124172123</v>
       </c>
       <c r="C38">
-        <v>161.7102886069344</v>
+        <v>158.8746749736826</v>
       </c>
       <c r="D38">
-        <v>246.8482886069344</v>
+        <v>246.4706749736826</v>
       </c>
       <c r="E38">
-        <v>76.58799999999999</v>
+        <v>79.04599999999999</v>
       </c>
       <c r="F38">
-        <v>88.488</v>
+        <v>90.946</v>
       </c>
       <c r="G38">
         <v>3.35</v>
@@ -4403,45 +4403,45 @@
         <v>36.448</v>
       </c>
       <c r="M38">
-        <v>4.734108</v>
+        <v>4.9383678</v>
       </c>
       <c r="N38">
-        <v>31.713892</v>
+        <v>31.5096322</v>
       </c>
       <c r="O38">
-        <v>4.7570838</v>
+        <v>4.726444829999999</v>
       </c>
       <c r="P38">
-        <v>26.9568082</v>
+        <v>26.78318737</v>
       </c>
       <c r="Q38">
-        <v>27.8088082</v>
+        <v>27.63518737</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1045693912034613</v>
+        <v>0.1054075733995575</v>
       </c>
       <c r="T38">
-        <v>1.076382038849091</v>
+        <v>1.091733640128022</v>
       </c>
       <c r="U38">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V38">
         <v>0.15</v>
       </c>
       <c r="W38">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y38">
-        <v>7.699021653075934</v>
+        <v>7.380576230065326</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08348412124172123</v>
+        <v>0.08342803211322722</v>
       </c>
       <c r="C39">
-        <v>158.8746749736826</v>
+        <v>156.5287895494841</v>
       </c>
       <c r="D39">
-        <v>246.4706749736826</v>
+        <v>246.5827895494841</v>
       </c>
       <c r="E39">
-        <v>79.04599999999999</v>
+        <v>81.504</v>
       </c>
       <c r="F39">
-        <v>90.946</v>
+        <v>93.40400000000001</v>
       </c>
       <c r="G39">
         <v>3.35</v>
@@ -4485,28 +4485,28 @@
         <v>36.448</v>
       </c>
       <c r="M39">
-        <v>4.9383678</v>
+        <v>5.071837200000001</v>
       </c>
       <c r="N39">
-        <v>31.5096322</v>
+        <v>31.3761628</v>
       </c>
       <c r="O39">
-        <v>4.726444829999999</v>
+        <v>4.706424419999999</v>
       </c>
       <c r="P39">
-        <v>26.78318737</v>
+        <v>26.66973838</v>
       </c>
       <c r="Q39">
-        <v>27.63518737</v>
+        <v>27.52173838</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1054075733995575</v>
+        <v>0.1062727937310117</v>
       </c>
       <c r="T39">
-        <v>1.091733640128022</v>
+        <v>1.107580454351434</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.380576230065326</v>
+        <v>7.186350539800448</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08342803211322722</v>
+        <v>0.08337194298473323</v>
       </c>
       <c r="C40">
-        <v>156.5287895494841</v>
+        <v>154.1830061690551</v>
       </c>
       <c r="D40">
-        <v>246.5827895494841</v>
+        <v>246.6950061690552</v>
       </c>
       <c r="E40">
-        <v>81.504</v>
+        <v>83.962</v>
       </c>
       <c r="F40">
-        <v>93.40400000000001</v>
+        <v>95.86200000000001</v>
       </c>
       <c r="G40">
         <v>3.35</v>
@@ -4567,28 +4567,28 @@
         <v>36.448</v>
       </c>
       <c r="M40">
-        <v>5.071837200000001</v>
+        <v>5.205306600000001</v>
       </c>
       <c r="N40">
-        <v>31.3761628</v>
+        <v>31.2426934</v>
       </c>
       <c r="O40">
-        <v>4.706424419999999</v>
+        <v>4.68640401</v>
       </c>
       <c r="P40">
-        <v>26.66973838</v>
+        <v>26.55628939</v>
       </c>
       <c r="Q40">
-        <v>27.52173838</v>
+        <v>27.40828939</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1062727937310117</v>
+        <v>0.1071663819421856</v>
       </c>
       <c r="T40">
-        <v>1.107580454351434</v>
+        <v>1.123946836254303</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.186350539800448</v>
+        <v>7.002085141344026</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08337194298473323</v>
+        <v>0.08331585385623924</v>
       </c>
       <c r="C41">
-        <v>154.1830061690551</v>
+        <v>151.8373249717758</v>
       </c>
       <c r="D41">
-        <v>246.6950061690552</v>
+        <v>246.8073249717759</v>
       </c>
       <c r="E41">
-        <v>83.962</v>
+        <v>86.42</v>
       </c>
       <c r="F41">
-        <v>95.86200000000001</v>
+        <v>98.32000000000001</v>
       </c>
       <c r="G41">
         <v>3.35</v>
@@ -4649,28 +4649,28 @@
         <v>36.448</v>
       </c>
       <c r="M41">
-        <v>5.205306600000001</v>
+        <v>5.338776</v>
       </c>
       <c r="N41">
-        <v>31.2426934</v>
+        <v>31.109224</v>
       </c>
       <c r="O41">
-        <v>4.68640401</v>
+        <v>4.6663836</v>
       </c>
       <c r="P41">
-        <v>26.55628939</v>
+        <v>26.4428404</v>
       </c>
       <c r="Q41">
-        <v>27.40828939</v>
+        <v>27.2948404</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1071663819421856</v>
+        <v>0.1080897564270654</v>
       </c>
       <c r="T41">
-        <v>1.123946836254303</v>
+        <v>1.140858764220601</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.002085141344026</v>
+        <v>6.827033012810427</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08331585385623924</v>
+        <v>0.08325976472774524</v>
       </c>
       <c r="C42">
-        <v>151.8373249717758</v>
+        <v>149.4917460972799</v>
       </c>
       <c r="D42">
-        <v>246.8073249717759</v>
+        <v>246.9197460972799</v>
       </c>
       <c r="E42">
-        <v>86.42</v>
+        <v>88.878</v>
       </c>
       <c r="F42">
-        <v>98.32000000000001</v>
+        <v>100.778</v>
       </c>
       <c r="G42">
         <v>3.35</v>
@@ -4731,28 +4731,28 @@
         <v>36.448</v>
       </c>
       <c r="M42">
-        <v>5.338776</v>
+        <v>5.4722454</v>
       </c>
       <c r="N42">
-        <v>31.109224</v>
+        <v>30.9757546</v>
       </c>
       <c r="O42">
-        <v>4.6663836</v>
+        <v>4.64636319</v>
       </c>
       <c r="P42">
-        <v>26.4428404</v>
+        <v>26.32939141</v>
       </c>
       <c r="Q42">
-        <v>27.2948404</v>
+        <v>27.18139141</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1080897564270654</v>
+        <v>0.1090444317419411</v>
       </c>
       <c r="T42">
-        <v>1.140858764220601</v>
+        <v>1.158343977880672</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.827033012810427</v>
+        <v>6.660520012497978</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08325976472774524</v>
+        <v>0.08320367559925124</v>
       </c>
       <c r="C43">
-        <v>149.4917460972799</v>
+        <v>147.1462696854555</v>
       </c>
       <c r="D43">
-        <v>246.9197460972799</v>
+        <v>247.0322696854556</v>
       </c>
       <c r="E43">
-        <v>88.878</v>
+        <v>91.33600000000001</v>
       </c>
       <c r="F43">
-        <v>100.778</v>
+        <v>103.236</v>
       </c>
       <c r="G43">
         <v>3.35</v>
@@ -4813,28 +4813,28 @@
         <v>36.448</v>
       </c>
       <c r="M43">
-        <v>5.4722454</v>
+        <v>5.605714800000001</v>
       </c>
       <c r="N43">
-        <v>30.9757546</v>
+        <v>30.8422852</v>
       </c>
       <c r="O43">
-        <v>4.64636319</v>
+        <v>4.62634278</v>
       </c>
       <c r="P43">
-        <v>26.32939141</v>
+        <v>26.21594242</v>
       </c>
       <c r="Q43">
-        <v>27.18139141</v>
+        <v>27.06794242</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1090444317419411</v>
+        <v>0.1100320268952608</v>
       </c>
       <c r="T43">
-        <v>1.158343977880672</v>
+        <v>1.176432129942814</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.660520012497978</v>
+        <v>6.501936202676596</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08320367559925125</v>
+        <v>0.08314758647075723</v>
       </c>
       <c r="C44">
-        <v>147.1462696854555</v>
+        <v>144.8008958764461</v>
       </c>
       <c r="D44">
-        <v>247.0322696854555</v>
+        <v>247.1448958764462</v>
       </c>
       <c r="E44">
-        <v>91.336</v>
+        <v>93.794</v>
       </c>
       <c r="F44">
-        <v>103.236</v>
+        <v>105.694</v>
       </c>
       <c r="G44">
         <v>3.35</v>
@@ -4895,28 +4895,28 @@
         <v>36.448</v>
       </c>
       <c r="M44">
-        <v>5.6057148</v>
+        <v>5.7391842</v>
       </c>
       <c r="N44">
-        <v>30.8422852</v>
+        <v>30.7088158</v>
       </c>
       <c r="O44">
-        <v>4.62634278</v>
+        <v>4.60632237</v>
       </c>
       <c r="P44">
-        <v>26.21594242</v>
+        <v>26.10249343</v>
       </c>
       <c r="Q44">
-        <v>27.06794242</v>
+        <v>26.95449343</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1100320268952608</v>
+        <v>0.1110542745101004</v>
       </c>
       <c r="T44">
-        <v>1.176432129942813</v>
+        <v>1.195154954007136</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.501936202676597</v>
+        <v>6.350728384009699</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08314758647075723</v>
+        <v>0.08309149734226323</v>
       </c>
       <c r="C45">
-        <v>144.8008958764461</v>
+        <v>142.4556248106509</v>
       </c>
       <c r="D45">
-        <v>247.1448958764462</v>
+        <v>247.2576248106509</v>
       </c>
       <c r="E45">
-        <v>93.794</v>
+        <v>96.252</v>
       </c>
       <c r="F45">
-        <v>105.694</v>
+        <v>108.152</v>
       </c>
       <c r="G45">
         <v>3.35</v>
@@ -4977,28 +4977,28 @@
         <v>36.448</v>
       </c>
       <c r="M45">
-        <v>5.7391842</v>
+        <v>5.8726536</v>
       </c>
       <c r="N45">
-        <v>30.7088158</v>
+        <v>30.5753464</v>
       </c>
       <c r="O45">
-        <v>4.60632237</v>
+        <v>4.58630196</v>
       </c>
       <c r="P45">
-        <v>26.10249343</v>
+        <v>25.98904444</v>
       </c>
       <c r="Q45">
-        <v>26.95449343</v>
+        <v>26.84104444</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1110542745101004</v>
+        <v>0.1121130309683272</v>
       </c>
       <c r="T45">
-        <v>1.195154954007136</v>
+        <v>1.214546450359469</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.350728384009699</v>
+        <v>6.206393648009478</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08309149734226323</v>
+        <v>0.08341790821376925</v>
       </c>
       <c r="C46">
-        <v>142.4556248106509</v>
+        <v>139.3430367216295</v>
       </c>
       <c r="D46">
-        <v>247.2576248106509</v>
+        <v>246.6030367216295</v>
       </c>
       <c r="E46">
-        <v>96.252</v>
+        <v>98.71000000000001</v>
       </c>
       <c r="F46">
-        <v>108.152</v>
+        <v>110.61</v>
       </c>
       <c r="G46">
         <v>3.35</v>
@@ -5059,45 +5059,45 @@
         <v>36.448</v>
       </c>
       <c r="M46">
-        <v>5.8726536</v>
+        <v>6.116733000000001</v>
       </c>
       <c r="N46">
-        <v>30.5753464</v>
+        <v>30.331267</v>
       </c>
       <c r="O46">
-        <v>4.58630196</v>
+        <v>4.54969005</v>
       </c>
       <c r="P46">
-        <v>25.98904444</v>
+        <v>25.78157695</v>
       </c>
       <c r="Q46">
-        <v>26.84104444</v>
+        <v>26.63357695</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1121130309683272</v>
+        <v>0.1132102876613986</v>
       </c>
       <c r="T46">
-        <v>1.214546450359469</v>
+        <v>1.234643092033706</v>
       </c>
       <c r="U46">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V46">
         <v>0.15</v>
       </c>
       <c r="W46">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>6.206393648009478</v>
+        <v>5.958736469288425</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08341790821376925</v>
+        <v>0.08337031908527524</v>
       </c>
       <c r="C47">
-        <v>139.3430367216295</v>
+        <v>136.9802566000128</v>
       </c>
       <c r="D47">
-        <v>246.6030367216295</v>
+        <v>246.6982566000128</v>
       </c>
       <c r="E47">
-        <v>98.71000000000001</v>
+        <v>101.168</v>
       </c>
       <c r="F47">
-        <v>110.61</v>
+        <v>113.068</v>
       </c>
       <c r="G47">
         <v>3.35</v>
@@ -5141,28 +5141,28 @@
         <v>36.448</v>
       </c>
       <c r="M47">
-        <v>6.116733000000001</v>
+        <v>6.252660400000001</v>
       </c>
       <c r="N47">
-        <v>30.331267</v>
+        <v>30.1953396</v>
       </c>
       <c r="O47">
-        <v>4.54969005</v>
+        <v>4.52930094</v>
       </c>
       <c r="P47">
-        <v>25.78157695</v>
+        <v>25.66603866</v>
       </c>
       <c r="Q47">
-        <v>26.63357695</v>
+        <v>26.51803866</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1132102876613986</v>
+        <v>0.1143481834912504</v>
       </c>
       <c r="T47">
-        <v>1.234643092033706</v>
+        <v>1.255484053769952</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.958736469288425</v>
+        <v>5.829198719956068</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08337031908527524</v>
+        <v>0.08332272995678124</v>
       </c>
       <c r="C48">
-        <v>136.9802566000128</v>
+        <v>134.6175500405683</v>
       </c>
       <c r="D48">
-        <v>246.6982566000128</v>
+        <v>246.7935500405683</v>
       </c>
       <c r="E48">
-        <v>101.168</v>
+        <v>103.626</v>
       </c>
       <c r="F48">
-        <v>113.068</v>
+        <v>115.526</v>
       </c>
       <c r="G48">
         <v>3.35</v>
@@ -5223,28 +5223,28 @@
         <v>36.448</v>
       </c>
       <c r="M48">
-        <v>6.252660400000001</v>
+        <v>6.388587800000001</v>
       </c>
       <c r="N48">
-        <v>30.1953396</v>
+        <v>30.0594122</v>
       </c>
       <c r="O48">
-        <v>4.52930094</v>
+        <v>4.50891183</v>
       </c>
       <c r="P48">
-        <v>25.66603866</v>
+        <v>25.55050037</v>
       </c>
       <c r="Q48">
-        <v>26.51803866</v>
+        <v>26.40250037</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1143481834912504</v>
+        <v>0.1155290187863797</v>
       </c>
       <c r="T48">
-        <v>1.255484053769952</v>
+        <v>1.277111466892471</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.829198719956068</v>
+        <v>5.705173215276152</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08332272995678124</v>
+        <v>0.08327514082828724</v>
       </c>
       <c r="C49">
-        <v>134.6175500405683</v>
+        <v>132.2549171285746</v>
       </c>
       <c r="D49">
-        <v>246.7935500405683</v>
+        <v>246.8889171285747</v>
       </c>
       <c r="E49">
-        <v>103.626</v>
+        <v>106.084</v>
       </c>
       <c r="F49">
-        <v>115.526</v>
+        <v>117.984</v>
       </c>
       <c r="G49">
         <v>3.35</v>
@@ -5305,28 +5305,28 @@
         <v>36.448</v>
       </c>
       <c r="M49">
-        <v>6.388587800000001</v>
+        <v>6.524515200000001</v>
       </c>
       <c r="N49">
-        <v>30.0594122</v>
+        <v>29.9234848</v>
       </c>
       <c r="O49">
-        <v>4.50891183</v>
+        <v>4.48852272</v>
       </c>
       <c r="P49">
-        <v>25.55050037</v>
+        <v>25.43496208</v>
       </c>
       <c r="Q49">
-        <v>26.40250037</v>
+        <v>26.28696208</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1155290187863797</v>
+        <v>0.1167552708236293</v>
       </c>
       <c r="T49">
-        <v>1.277111466892471</v>
+        <v>1.299570703596626</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.705173215276152</v>
+        <v>5.586315439957898</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08327514082828724</v>
+        <v>0.08322755169979323</v>
       </c>
       <c r="C50">
-        <v>132.2549171285747</v>
+        <v>129.8923579494426</v>
       </c>
       <c r="D50">
-        <v>246.8889171285747</v>
+        <v>246.9843579494426</v>
       </c>
       <c r="E50">
-        <v>106.084</v>
+        <v>108.542</v>
       </c>
       <c r="F50">
-        <v>117.984</v>
+        <v>120.442</v>
       </c>
       <c r="G50">
         <v>3.35</v>
@@ -5387,28 +5387,28 @@
         <v>36.448</v>
       </c>
       <c r="M50">
-        <v>6.5245152</v>
+        <v>6.660442600000001</v>
       </c>
       <c r="N50">
-        <v>29.9234848</v>
+        <v>29.7875574</v>
       </c>
       <c r="O50">
-        <v>4.48852272</v>
+        <v>4.46813361</v>
       </c>
       <c r="P50">
-        <v>25.43496208</v>
+        <v>25.31942379</v>
       </c>
       <c r="Q50">
-        <v>26.28696208</v>
+        <v>26.17142379</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1167552708236293</v>
+        <v>0.1180296111760652</v>
       </c>
       <c r="T50">
-        <v>1.299570703596626</v>
+        <v>1.322910694681335</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.586315439957899</v>
+        <v>5.472309002407737</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08322755169979323</v>
+        <v>0.08317996257129924</v>
       </c>
       <c r="C51">
-        <v>129.8923579494426</v>
+        <v>127.5298725887145</v>
       </c>
       <c r="D51">
-        <v>246.9843579494426</v>
+        <v>247.0798725887146</v>
       </c>
       <c r="E51">
-        <v>108.542</v>
+        <v>111</v>
       </c>
       <c r="F51">
-        <v>120.442</v>
+        <v>122.9</v>
       </c>
       <c r="G51">
         <v>3.35</v>
@@ -5469,28 +5469,28 @@
         <v>36.448</v>
       </c>
       <c r="M51">
-        <v>6.660442600000001</v>
+        <v>6.79637</v>
       </c>
       <c r="N51">
-        <v>29.7875574</v>
+        <v>29.65163</v>
       </c>
       <c r="O51">
-        <v>4.46813361</v>
+        <v>4.4477445</v>
       </c>
       <c r="P51">
-        <v>25.31942379</v>
+        <v>25.2038855</v>
       </c>
       <c r="Q51">
-        <v>26.17142379</v>
+        <v>26.0558855</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1180296111760652</v>
+        <v>0.1193549251425985</v>
       </c>
       <c r="T51">
-        <v>1.322910694681335</v>
+        <v>1.347184285409433</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.472309002407737</v>
+        <v>5.362862822359583</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08317996257129924</v>
+        <v>0.08313237344280525</v>
       </c>
       <c r="C52">
-        <v>127.5298725887145</v>
+        <v>125.1674611320658</v>
       </c>
       <c r="D52">
-        <v>247.0798725887146</v>
+        <v>247.1754611320658</v>
       </c>
       <c r="E52">
-        <v>111</v>
+        <v>113.458</v>
       </c>
       <c r="F52">
-        <v>122.9</v>
+        <v>125.358</v>
       </c>
       <c r="G52">
         <v>3.35</v>
@@ -5551,28 +5551,28 @@
         <v>36.448</v>
       </c>
       <c r="M52">
-        <v>6.79637</v>
+        <v>6.9322974</v>
       </c>
       <c r="N52">
-        <v>29.65163</v>
+        <v>29.5157026</v>
       </c>
       <c r="O52">
-        <v>4.4477445</v>
+        <v>4.42735539</v>
       </c>
       <c r="P52">
-        <v>25.2038855</v>
+        <v>25.08834721</v>
       </c>
       <c r="Q52">
-        <v>26.0558855</v>
+        <v>25.94034721</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1193549251425985</v>
+        <v>0.1207343335567454</v>
       </c>
       <c r="T52">
-        <v>1.347184285409433</v>
+        <v>1.37244863494276</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.362862822359583</v>
+        <v>5.25770864937214</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08313237344280525</v>
+        <v>0.08308478431431125</v>
       </c>
       <c r="C53">
-        <v>125.1674611320658</v>
+        <v>122.8051236653039</v>
       </c>
       <c r="D53">
-        <v>247.1754611320658</v>
+        <v>247.2711236653039</v>
       </c>
       <c r="E53">
-        <v>113.458</v>
+        <v>115.916</v>
       </c>
       <c r="F53">
-        <v>125.358</v>
+        <v>127.816</v>
       </c>
       <c r="G53">
         <v>3.35</v>
@@ -5633,28 +5633,28 @@
         <v>36.448</v>
       </c>
       <c r="M53">
-        <v>6.9322974</v>
+        <v>7.068224800000001</v>
       </c>
       <c r="N53">
-        <v>29.5157026</v>
+        <v>29.3797752</v>
       </c>
       <c r="O53">
-        <v>4.42735539</v>
+        <v>4.40696628</v>
       </c>
       <c r="P53">
-        <v>25.08834721</v>
+        <v>24.97280892</v>
       </c>
       <c r="Q53">
-        <v>25.94034721</v>
+        <v>25.82480892</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1207343335567454</v>
+        <v>0.1221712173214818</v>
       </c>
       <c r="T53">
-        <v>1.37244863494276</v>
+        <v>1.398765665706641</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.25770864937214</v>
+        <v>5.156598867653444</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08308478431431125</v>
+        <v>0.08303719518581724</v>
       </c>
       <c r="C54">
-        <v>122.8051236653039</v>
+        <v>120.4428602743695</v>
       </c>
       <c r="D54">
-        <v>247.2711236653039</v>
+        <v>247.3668602743695</v>
       </c>
       <c r="E54">
-        <v>115.916</v>
+        <v>118.374</v>
       </c>
       <c r="F54">
-        <v>127.816</v>
+        <v>130.274</v>
       </c>
       <c r="G54">
         <v>3.35</v>
@@ -5715,28 +5715,28 @@
         <v>36.448</v>
       </c>
       <c r="M54">
-        <v>7.068224800000001</v>
+        <v>7.2041522</v>
       </c>
       <c r="N54">
-        <v>29.3797752</v>
+        <v>29.2438478</v>
       </c>
       <c r="O54">
-        <v>4.40696628</v>
+        <v>4.38657717</v>
       </c>
       <c r="P54">
-        <v>24.97280892</v>
+        <v>24.85727063</v>
       </c>
       <c r="Q54">
-        <v>25.82480892</v>
+        <v>25.70927063</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1221712173214818</v>
+        <v>0.1236692450762069</v>
       </c>
       <c r="T54">
-        <v>1.398765665706641</v>
+        <v>1.42620257012005</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.156598867653444</v>
+        <v>5.059304549395833</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08303719518581724</v>
+        <v>0.08298960605732325</v>
       </c>
       <c r="C55">
-        <v>120.4428602743695</v>
+        <v>118.0806710453362</v>
       </c>
       <c r="D55">
-        <v>247.3668602743695</v>
+        <v>247.4626710453362</v>
       </c>
       <c r="E55">
-        <v>118.374</v>
+        <v>120.832</v>
       </c>
       <c r="F55">
-        <v>130.274</v>
+        <v>132.732</v>
       </c>
       <c r="G55">
         <v>3.35</v>
@@ -5797,28 +5797,28 @@
         <v>36.448</v>
       </c>
       <c r="M55">
-        <v>7.2041522</v>
+        <v>7.340079600000002</v>
       </c>
       <c r="N55">
-        <v>29.2438478</v>
+        <v>29.1079204</v>
       </c>
       <c r="O55">
-        <v>4.38657717</v>
+        <v>4.36618806</v>
       </c>
       <c r="P55">
-        <v>24.85727063</v>
+        <v>24.74173234</v>
       </c>
       <c r="Q55">
-        <v>25.70927063</v>
+        <v>25.59373234</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1236692450762069</v>
+        <v>0.1252324044724419</v>
       </c>
       <c r="T55">
-        <v>1.42620257012005</v>
+        <v>1.454832383420998</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.059304549395833</v>
+        <v>4.96561372440702</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08298960605732325</v>
+        <v>0.08294201692882927</v>
       </c>
       <c r="C56">
-        <v>118.0806710453362</v>
+        <v>115.7185560644112</v>
       </c>
       <c r="D56">
-        <v>247.4626710453362</v>
+        <v>247.5585560644113</v>
       </c>
       <c r="E56">
-        <v>120.832</v>
+        <v>123.29</v>
       </c>
       <c r="F56">
-        <v>132.732</v>
+        <v>135.19</v>
       </c>
       <c r="G56">
         <v>3.35</v>
@@ -5879,28 +5879,28 @@
         <v>36.448</v>
       </c>
       <c r="M56">
-        <v>7.340079600000002</v>
+        <v>7.476007000000002</v>
       </c>
       <c r="N56">
-        <v>29.1079204</v>
+        <v>28.971993</v>
       </c>
       <c r="O56">
-        <v>4.36618806</v>
+        <v>4.34579895</v>
       </c>
       <c r="P56">
-        <v>24.74173234</v>
+        <v>24.62619405</v>
       </c>
       <c r="Q56">
-        <v>25.59373234</v>
+        <v>25.47819405</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1252324044724419</v>
+        <v>0.1268650376196206</v>
       </c>
       <c r="T56">
-        <v>1.454832383420998</v>
+        <v>1.484734632868655</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.96561372440702</v>
+        <v>4.87532983850871</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08294201692882927</v>
+        <v>0.08289442780033525</v>
       </c>
       <c r="C57">
-        <v>115.7185560644112</v>
+        <v>113.3565154179355</v>
       </c>
       <c r="D57">
-        <v>247.5585560644113</v>
+        <v>247.6545154179355</v>
       </c>
       <c r="E57">
-        <v>123.29</v>
+        <v>125.748</v>
       </c>
       <c r="F57">
-        <v>135.19</v>
+        <v>137.648</v>
       </c>
       <c r="G57">
         <v>3.35</v>
@@ -5961,28 +5961,28 @@
         <v>36.448</v>
       </c>
       <c r="M57">
-        <v>7.476007000000002</v>
+        <v>7.611934400000002</v>
       </c>
       <c r="N57">
-        <v>28.971993</v>
+        <v>28.8360656</v>
       </c>
       <c r="O57">
-        <v>4.34579895</v>
+        <v>4.32540984</v>
       </c>
       <c r="P57">
-        <v>24.62619405</v>
+        <v>24.51065576</v>
       </c>
       <c r="Q57">
-        <v>25.47819405</v>
+        <v>25.36265576</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1268650376196206</v>
+        <v>0.1285718813643983</v>
       </c>
       <c r="T57">
-        <v>1.484734632868655</v>
+        <v>1.515996075473023</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.87532983850871</v>
+        <v>4.78827037710677</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08289442780033525</v>
+        <v>0.08284683867184126</v>
       </c>
       <c r="C58">
-        <v>113.3565154179355</v>
+        <v>110.9945491923835</v>
       </c>
       <c r="D58">
-        <v>247.6545154179355</v>
+        <v>247.7505491923835</v>
       </c>
       <c r="E58">
-        <v>125.748</v>
+        <v>128.206</v>
       </c>
       <c r="F58">
-        <v>137.648</v>
+        <v>140.106</v>
       </c>
       <c r="G58">
         <v>3.35</v>
@@ -6043,28 +6043,28 @@
         <v>36.448</v>
       </c>
       <c r="M58">
-        <v>7.611934400000002</v>
+        <v>7.747861800000002</v>
       </c>
       <c r="N58">
-        <v>28.8360656</v>
+        <v>28.7001382</v>
       </c>
       <c r="O58">
-        <v>4.32540984</v>
+        <v>4.30502073</v>
       </c>
       <c r="P58">
-        <v>24.51065576</v>
+        <v>24.39511747</v>
       </c>
       <c r="Q58">
-        <v>25.36265576</v>
+        <v>25.24711747</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1285718813643983</v>
+        <v>0.1303581131903285</v>
       </c>
       <c r="T58">
-        <v>1.515996075473023</v>
+        <v>1.548711538663641</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.78827037710677</v>
+        <v>4.704265633648756</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08284683867184126</v>
+        <v>0.08279924954334726</v>
       </c>
       <c r="C59">
-        <v>110.9945491923835</v>
+        <v>108.6326574743642</v>
       </c>
       <c r="D59">
-        <v>247.7505491923835</v>
+        <v>247.8466574743642</v>
       </c>
       <c r="E59">
-        <v>128.206</v>
+        <v>130.664</v>
       </c>
       <c r="F59">
-        <v>140.106</v>
+        <v>142.564</v>
       </c>
       <c r="G59">
         <v>3.35</v>
@@ -6125,28 +6125,28 @@
         <v>36.448</v>
       </c>
       <c r="M59">
-        <v>7.747861800000002</v>
+        <v>7.883789200000002</v>
       </c>
       <c r="N59">
-        <v>28.7001382</v>
+        <v>28.5642108</v>
       </c>
       <c r="O59">
-        <v>4.30502073</v>
+        <v>4.28463162</v>
       </c>
       <c r="P59">
-        <v>24.39511747</v>
+        <v>24.27957918</v>
       </c>
       <c r="Q59">
-        <v>25.24711747</v>
+        <v>25.13157918</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1303581131903285</v>
+        <v>0.1322294036746363</v>
       </c>
       <c r="T59">
-        <v>1.548711538663641</v>
+        <v>1.582984881053813</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.704265633648756</v>
+        <v>4.623157605482398</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08279924954334725</v>
+        <v>0.08275166041485325</v>
       </c>
       <c r="C60">
-        <v>108.6326574743642</v>
+        <v>106.270840350621</v>
       </c>
       <c r="D60">
-        <v>247.8466574743642</v>
+        <v>247.942840350621</v>
       </c>
       <c r="E60">
-        <v>130.664</v>
+        <v>133.122</v>
       </c>
       <c r="F60">
-        <v>142.564</v>
+        <v>145.022</v>
       </c>
       <c r="G60">
         <v>3.35</v>
@@ -6207,28 +6207,28 @@
         <v>36.448</v>
       </c>
       <c r="M60">
-        <v>7.8837892</v>
+        <v>8.019716600000001</v>
       </c>
       <c r="N60">
-        <v>28.5642108</v>
+        <v>28.4282834</v>
       </c>
       <c r="O60">
-        <v>4.28463162</v>
+        <v>4.26424251</v>
       </c>
       <c r="P60">
-        <v>24.27957918</v>
+        <v>24.16404089</v>
       </c>
       <c r="Q60">
-        <v>25.13157918</v>
+        <v>25.01604089</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1322294036746363</v>
+        <v>0.1341919766215933</v>
       </c>
       <c r="T60">
-        <v>1.582984881053813</v>
+        <v>1.61893009380448</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.623157605482399</v>
+        <v>4.544799001999646</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08275166041485325</v>
+        <v>0.08397907128635926</v>
       </c>
       <c r="C61">
-        <v>106.270840350621</v>
+        <v>101.3557384121047</v>
       </c>
       <c r="D61">
-        <v>247.942840350621</v>
+        <v>245.4857384121047</v>
       </c>
       <c r="E61">
-        <v>133.122</v>
+        <v>135.58</v>
       </c>
       <c r="F61">
-        <v>145.022</v>
+        <v>147.48</v>
       </c>
       <c r="G61">
         <v>3.35</v>
@@ -6289,45 +6289,45 @@
         <v>36.448</v>
       </c>
       <c r="M61">
-        <v>8.019716600000001</v>
+        <v>8.524343999999999</v>
       </c>
       <c r="N61">
-        <v>28.4282834</v>
+        <v>27.923656</v>
       </c>
       <c r="O61">
-        <v>4.26424251</v>
+        <v>4.1885484</v>
       </c>
       <c r="P61">
-        <v>24.16404089</v>
+        <v>23.7351076</v>
       </c>
       <c r="Q61">
-        <v>25.01604089</v>
+        <v>24.5871076</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1341919766215933</v>
+        <v>0.1362526782158981</v>
       </c>
       <c r="T61">
-        <v>1.61893009380448</v>
+        <v>1.656672567192681</v>
       </c>
       <c r="U61">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V61">
         <v>0.15</v>
       </c>
       <c r="W61">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y61">
-        <v>4.544799001999646</v>
+        <v>4.27575423985705</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08397907128635926</v>
+        <v>0.08395273215786526</v>
       </c>
       <c r="C62">
-        <v>101.3557384121047</v>
+        <v>98.94995418019923</v>
       </c>
       <c r="D62">
-        <v>245.4857384121047</v>
+        <v>245.5379541801993</v>
       </c>
       <c r="E62">
-        <v>135.58</v>
+        <v>138.038</v>
       </c>
       <c r="F62">
-        <v>147.48</v>
+        <v>149.938</v>
       </c>
       <c r="G62">
         <v>3.35</v>
@@ -6371,28 +6371,28 @@
         <v>36.448</v>
       </c>
       <c r="M62">
-        <v>8.524343999999999</v>
+        <v>8.666416400000001</v>
       </c>
       <c r="N62">
-        <v>27.923656</v>
+        <v>27.7815836</v>
       </c>
       <c r="O62">
-        <v>4.1885484</v>
+        <v>4.167237539999999</v>
       </c>
       <c r="P62">
-        <v>23.7351076</v>
+        <v>23.61434606</v>
       </c>
       <c r="Q62">
-        <v>24.5871076</v>
+        <v>24.46634606</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1362526782158981</v>
+        <v>0.1384190568150391</v>
       </c>
       <c r="T62">
-        <v>1.656672567192681</v>
+        <v>1.696350552036687</v>
       </c>
       <c r="U62">
         <v>0.0578</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.27575423985705</v>
+        <v>4.205659908056114</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08395273215786526</v>
+        <v>0.08392639302937127</v>
       </c>
       <c r="C63">
-        <v>98.94995418019923</v>
+        <v>96.5441921660121</v>
       </c>
       <c r="D63">
-        <v>245.5379541801993</v>
+        <v>245.5901921660121</v>
       </c>
       <c r="E63">
-        <v>138.038</v>
+        <v>140.496</v>
       </c>
       <c r="F63">
-        <v>149.938</v>
+        <v>152.396</v>
       </c>
       <c r="G63">
         <v>3.35</v>
@@ -6453,28 +6453,28 @@
         <v>36.448</v>
       </c>
       <c r="M63">
-        <v>8.666416400000001</v>
+        <v>8.808488800000001</v>
       </c>
       <c r="N63">
-        <v>27.7815836</v>
+        <v>27.6395112</v>
       </c>
       <c r="O63">
-        <v>4.167237539999999</v>
+        <v>4.14592668</v>
       </c>
       <c r="P63">
-        <v>23.61434606</v>
+        <v>23.49358452</v>
       </c>
       <c r="Q63">
-        <v>24.46634606</v>
+        <v>24.34558452</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1384190568150391</v>
+        <v>0.1406994553404507</v>
       </c>
       <c r="T63">
-        <v>1.696350552036687</v>
+        <v>1.738116851872483</v>
       </c>
       <c r="U63">
         <v>0.0578</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.205659908056114</v>
+        <v>4.137826683732628</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08392639302937127</v>
+        <v>0.08390005390087726</v>
       </c>
       <c r="C64">
-        <v>96.5441921660121</v>
+        <v>94.1384523837267</v>
       </c>
       <c r="D64">
-        <v>245.5901921660121</v>
+        <v>245.6424523837267</v>
       </c>
       <c r="E64">
-        <v>140.496</v>
+        <v>142.954</v>
       </c>
       <c r="F64">
-        <v>152.396</v>
+        <v>154.854</v>
       </c>
       <c r="G64">
         <v>3.35</v>
@@ -6535,28 +6535,28 @@
         <v>36.448</v>
       </c>
       <c r="M64">
-        <v>8.808488800000001</v>
+        <v>8.950561200000001</v>
       </c>
       <c r="N64">
-        <v>27.6395112</v>
+        <v>27.4974388</v>
       </c>
       <c r="O64">
-        <v>4.14592668</v>
+        <v>4.12461582</v>
       </c>
       <c r="P64">
-        <v>23.49358452</v>
+        <v>23.37282298</v>
       </c>
       <c r="Q64">
-        <v>24.34558452</v>
+        <v>24.22482298</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1406994553404507</v>
+        <v>0.1431031186510196</v>
       </c>
       <c r="T64">
-        <v>1.738116851872483</v>
+        <v>1.782140789537241</v>
       </c>
       <c r="U64">
         <v>0.0578</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.137826683732628</v>
+        <v>4.072146895101952</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08390005390087726</v>
+        <v>0.08387371477238326</v>
       </c>
       <c r="C65">
-        <v>94.1384523837267</v>
+        <v>91.73273484753861</v>
       </c>
       <c r="D65">
-        <v>245.6424523837267</v>
+        <v>245.6947348475386</v>
       </c>
       <c r="E65">
-        <v>142.954</v>
+        <v>145.412</v>
       </c>
       <c r="F65">
-        <v>154.854</v>
+        <v>157.312</v>
       </c>
       <c r="G65">
         <v>3.35</v>
@@ -6617,28 +6617,28 @@
         <v>36.448</v>
       </c>
       <c r="M65">
-        <v>8.950561200000001</v>
+        <v>9.092633600000001</v>
       </c>
       <c r="N65">
-        <v>27.4974388</v>
+        <v>27.3553664</v>
       </c>
       <c r="O65">
-        <v>4.12461582</v>
+        <v>4.10330496</v>
       </c>
       <c r="P65">
-        <v>23.37282298</v>
+        <v>23.25206144</v>
       </c>
       <c r="Q65">
-        <v>24.22482298</v>
+        <v>24.10406144</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1431031186510196</v>
+        <v>0.1456403188121757</v>
       </c>
       <c r="T65">
-        <v>1.782140789537241</v>
+        <v>1.828610501516708</v>
       </c>
       <c r="U65">
         <v>0.0578</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.072146895101952</v>
+        <v>4.008519599865984</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08387371477238326</v>
+        <v>0.08578112564388926</v>
       </c>
       <c r="C66">
-        <v>91.73273484753861</v>
+        <v>85.54525316638376</v>
       </c>
       <c r="D66">
-        <v>245.6947348475386</v>
+        <v>241.9652531663838</v>
       </c>
       <c r="E66">
-        <v>145.412</v>
+        <v>147.87</v>
       </c>
       <c r="F66">
-        <v>157.312</v>
+        <v>159.77</v>
       </c>
       <c r="G66">
         <v>3.35</v>
@@ -6699,45 +6699,45 @@
         <v>36.448</v>
       </c>
       <c r="M66">
-        <v>9.092633600000001</v>
+        <v>9.793901</v>
       </c>
       <c r="N66">
-        <v>27.3553664</v>
+        <v>26.654099</v>
       </c>
       <c r="O66">
-        <v>4.10330496</v>
+        <v>3.99811485</v>
       </c>
       <c r="P66">
-        <v>23.25206144</v>
+        <v>22.65598415</v>
       </c>
       <c r="Q66">
-        <v>24.10406144</v>
+        <v>23.50798415</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1456403188121757</v>
+        <v>0.1483225018396836</v>
       </c>
       <c r="T66">
-        <v>1.828610501516708</v>
+        <v>1.877735625609287</v>
       </c>
       <c r="U66">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V66">
         <v>0.15</v>
       </c>
       <c r="W66">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y66">
-        <v>4.008519599865984</v>
+        <v>3.721499737438637</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08578112564388926</v>
+        <v>0.08578453651539525</v>
       </c>
       <c r="C67">
-        <v>85.54525316638376</v>
+        <v>83.0806854415313</v>
       </c>
       <c r="D67">
-        <v>241.9652531663838</v>
+        <v>241.9586854415313</v>
       </c>
       <c r="E67">
-        <v>147.87</v>
+        <v>150.328</v>
       </c>
       <c r="F67">
-        <v>159.77</v>
+        <v>162.228</v>
       </c>
       <c r="G67">
         <v>3.35</v>
@@ -6781,28 +6781,28 @@
         <v>36.448</v>
       </c>
       <c r="M67">
-        <v>9.793901</v>
+        <v>9.944576400000001</v>
       </c>
       <c r="N67">
-        <v>26.654099</v>
+        <v>26.5034236</v>
       </c>
       <c r="O67">
-        <v>3.99811485</v>
+        <v>3.97551354</v>
       </c>
       <c r="P67">
-        <v>22.65598415</v>
+        <v>22.52791006</v>
       </c>
       <c r="Q67">
-        <v>23.50798415</v>
+        <v>23.37991006</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1483225018396836</v>
+        <v>0.1511624603393978</v>
       </c>
       <c r="T67">
-        <v>1.877735625609287</v>
+        <v>1.929750462883783</v>
       </c>
       <c r="U67">
         <v>0.0613</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.721499737438637</v>
+        <v>3.665113377780475</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08578453651539525</v>
+        <v>0.08578794738690126</v>
       </c>
       <c r="C68">
-        <v>83.0806854415313</v>
+        <v>80.61611807320799</v>
       </c>
       <c r="D68">
-        <v>241.9586854415313</v>
+        <v>241.952118073208</v>
       </c>
       <c r="E68">
-        <v>150.328</v>
+        <v>152.786</v>
       </c>
       <c r="F68">
-        <v>162.228</v>
+        <v>164.686</v>
       </c>
       <c r="G68">
         <v>3.35</v>
@@ -6863,28 +6863,28 @@
         <v>36.448</v>
       </c>
       <c r="M68">
-        <v>9.944576400000001</v>
+        <v>10.0952518</v>
       </c>
       <c r="N68">
-        <v>26.5034236</v>
+        <v>26.3527482</v>
       </c>
       <c r="O68">
-        <v>3.97551354</v>
+        <v>3.95291223</v>
       </c>
       <c r="P68">
-        <v>22.52791006</v>
+        <v>22.39983597</v>
       </c>
       <c r="Q68">
-        <v>23.37991006</v>
+        <v>23.25183597</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1511624603393978</v>
+        <v>0.1541745375360644</v>
       </c>
       <c r="T68">
-        <v>1.929750462883783</v>
+        <v>1.984917714538551</v>
       </c>
       <c r="U68">
         <v>0.0613</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.665113377780475</v>
+        <v>3.610410193037483</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08578794738690126</v>
+        <v>0.08579135825840727</v>
       </c>
       <c r="C69">
-        <v>80.61611807320799</v>
+        <v>78.15155106138485</v>
       </c>
       <c r="D69">
-        <v>241.952118073208</v>
+        <v>241.9455510613849</v>
       </c>
       <c r="E69">
-        <v>152.786</v>
+        <v>155.244</v>
       </c>
       <c r="F69">
-        <v>164.686</v>
+        <v>167.144</v>
       </c>
       <c r="G69">
         <v>3.35</v>
@@ -6945,28 +6945,28 @@
         <v>36.448</v>
       </c>
       <c r="M69">
-        <v>10.0952518</v>
+        <v>10.2459272</v>
       </c>
       <c r="N69">
-        <v>26.3527482</v>
+        <v>26.2020728</v>
       </c>
       <c r="O69">
-        <v>3.95291223</v>
+        <v>3.930310919999999</v>
       </c>
       <c r="P69">
-        <v>22.39983597</v>
+        <v>22.27176188</v>
       </c>
       <c r="Q69">
-        <v>23.25183597</v>
+        <v>23.12376188</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1541745375360644</v>
+        <v>0.1573748695575227</v>
       </c>
       <c r="T69">
-        <v>1.984917714538551</v>
+        <v>2.043532919421742</v>
       </c>
       <c r="U69">
         <v>0.0613</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.610410193037483</v>
+        <v>3.557315925492814</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08579135825840727</v>
+        <v>0.08579476912991327</v>
       </c>
       <c r="C70">
-        <v>78.15155106138485</v>
+        <v>75.68698440603291</v>
       </c>
       <c r="D70">
-        <v>241.9455510613849</v>
+        <v>241.9389844060329</v>
       </c>
       <c r="E70">
-        <v>155.244</v>
+        <v>157.702</v>
       </c>
       <c r="F70">
-        <v>167.144</v>
+        <v>169.602</v>
       </c>
       <c r="G70">
         <v>3.35</v>
@@ -7027,28 +7027,28 @@
         <v>36.448</v>
       </c>
       <c r="M70">
-        <v>10.2459272</v>
+        <v>10.3966026</v>
       </c>
       <c r="N70">
-        <v>26.2020728</v>
+        <v>26.0513974</v>
       </c>
       <c r="O70">
-        <v>3.930310919999999</v>
+        <v>3.90770961</v>
       </c>
       <c r="P70">
-        <v>22.27176188</v>
+        <v>22.14368779</v>
       </c>
       <c r="Q70">
-        <v>23.12376188</v>
+        <v>22.99568779</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1573748695575227</v>
+        <v>0.1607816746126235</v>
       </c>
       <c r="T70">
-        <v>2.043532919421742</v>
+        <v>2.105929750426429</v>
       </c>
       <c r="U70">
         <v>0.0613</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.557315925492814</v>
+        <v>3.505760622224802</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08579476912991327</v>
+        <v>0.08746418000141926</v>
       </c>
       <c r="C71">
-        <v>75.68698440603291</v>
+        <v>70.05723266598633</v>
       </c>
       <c r="D71">
-        <v>241.9389844060329</v>
+        <v>238.7672326659864</v>
       </c>
       <c r="E71">
-        <v>157.702</v>
+        <v>160.16</v>
       </c>
       <c r="F71">
-        <v>169.602</v>
+        <v>172.06</v>
       </c>
       <c r="G71">
         <v>3.35</v>
@@ -7109,45 +7109,45 @@
         <v>36.448</v>
       </c>
       <c r="M71">
-        <v>10.3966026</v>
+        <v>11.029046</v>
       </c>
       <c r="N71">
-        <v>26.0513974</v>
+        <v>25.418954</v>
       </c>
       <c r="O71">
-        <v>3.90770961</v>
+        <v>3.8128431</v>
       </c>
       <c r="P71">
-        <v>22.14368779</v>
+        <v>21.6061109</v>
       </c>
       <c r="Q71">
-        <v>22.99568779</v>
+        <v>22.4581109</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1607816746126235</v>
+        <v>0.1644156000047309</v>
       </c>
       <c r="T71">
-        <v>2.105929750426429</v>
+        <v>2.172486370164762</v>
       </c>
       <c r="U71">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V71">
         <v>0.15</v>
       </c>
       <c r="W71">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y71">
-        <v>3.505760622224802</v>
+        <v>3.304728260268385</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08746418000141926</v>
+        <v>0.08749139087292528</v>
       </c>
       <c r="C72">
-        <v>70.05723266598633</v>
+        <v>67.54822276487153</v>
       </c>
       <c r="D72">
-        <v>238.7672326659864</v>
+        <v>238.7162227648716</v>
       </c>
       <c r="E72">
-        <v>160.16</v>
+        <v>162.618</v>
       </c>
       <c r="F72">
-        <v>172.06</v>
+        <v>174.518</v>
       </c>
       <c r="G72">
         <v>3.35</v>
@@ -7191,28 +7191,28 @@
         <v>36.448</v>
       </c>
       <c r="M72">
-        <v>11.029046</v>
+        <v>11.1866038</v>
       </c>
       <c r="N72">
-        <v>25.418954</v>
+        <v>25.2613962</v>
       </c>
       <c r="O72">
-        <v>3.8128431</v>
+        <v>3.78920943</v>
       </c>
       <c r="P72">
-        <v>21.6061109</v>
+        <v>21.47218677</v>
       </c>
       <c r="Q72">
-        <v>22.4581109</v>
+        <v>22.32418677</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1644156000047309</v>
+        <v>0.1683001409411217</v>
       </c>
       <c r="T72">
-        <v>2.172486370164762</v>
+        <v>2.243633101609187</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.304728260268385</v>
+        <v>3.258182791813901</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08749139087292529</v>
+        <v>0.08751860174443127</v>
       </c>
       <c r="C73">
-        <v>67.54822276487153</v>
+        <v>65.03923465447076</v>
       </c>
       <c r="D73">
-        <v>238.7162227648715</v>
+        <v>238.6652346544708</v>
       </c>
       <c r="E73">
-        <v>162.618</v>
+        <v>165.076</v>
       </c>
       <c r="F73">
-        <v>174.518</v>
+        <v>176.976</v>
       </c>
       <c r="G73">
         <v>3.35</v>
@@ -7273,28 +7273,28 @@
         <v>36.448</v>
       </c>
       <c r="M73">
-        <v>11.1866038</v>
+        <v>11.3441616</v>
       </c>
       <c r="N73">
-        <v>25.2613962</v>
+        <v>25.1038384</v>
       </c>
       <c r="O73">
-        <v>3.78920943</v>
+        <v>3.76557576</v>
       </c>
       <c r="P73">
-        <v>21.47218677</v>
+        <v>21.33826264</v>
       </c>
       <c r="Q73">
-        <v>22.32418677</v>
+        <v>22.19026264</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1683001409411216</v>
+        <v>0.1724621490872545</v>
       </c>
       <c r="T73">
-        <v>2.243633101609186</v>
+        <v>2.319861742442499</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.258182791813902</v>
+        <v>3.212930253038708</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08751860174443127</v>
+        <v>0.08754581261593727</v>
       </c>
       <c r="C74">
-        <v>65.03923465447076</v>
+        <v>62.53026832082398</v>
       </c>
       <c r="D74">
-        <v>238.6652346544708</v>
+        <v>238.614268320824</v>
       </c>
       <c r="E74">
-        <v>165.076</v>
+        <v>167.534</v>
       </c>
       <c r="F74">
-        <v>176.976</v>
+        <v>179.434</v>
       </c>
       <c r="G74">
         <v>3.35</v>
@@ -7355,28 +7355,28 @@
         <v>36.448</v>
       </c>
       <c r="M74">
-        <v>11.3441616</v>
+        <v>11.5017194</v>
       </c>
       <c r="N74">
-        <v>25.1038384</v>
+        <v>24.9462806</v>
       </c>
       <c r="O74">
-        <v>3.76557576</v>
+        <v>3.74194209</v>
       </c>
       <c r="P74">
-        <v>21.33826264</v>
+        <v>21.20433851</v>
       </c>
       <c r="Q74">
-        <v>22.19026264</v>
+        <v>22.05633851</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1724621490872545</v>
+        <v>0.176932454133101</v>
       </c>
       <c r="T74">
-        <v>2.319861742442499</v>
+        <v>2.401736949263463</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.212930253038708</v>
+        <v>3.168917509846398</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08754581261593727</v>
+        <v>0.08757302348744328</v>
       </c>
       <c r="C75">
-        <v>62.53026832082398</v>
+        <v>60.021323749983</v>
       </c>
       <c r="D75">
-        <v>238.614268320824</v>
+        <v>238.563323749983</v>
       </c>
       <c r="E75">
-        <v>167.534</v>
+        <v>169.992</v>
       </c>
       <c r="F75">
-        <v>179.434</v>
+        <v>181.892</v>
       </c>
       <c r="G75">
         <v>3.35</v>
@@ -7437,28 +7437,28 @@
         <v>36.448</v>
       </c>
       <c r="M75">
-        <v>11.5017194</v>
+        <v>11.6592772</v>
       </c>
       <c r="N75">
-        <v>24.9462806</v>
+        <v>24.7887228</v>
       </c>
       <c r="O75">
-        <v>3.74194209</v>
+        <v>3.71830842</v>
       </c>
       <c r="P75">
-        <v>21.20433851</v>
+        <v>21.07041438</v>
       </c>
       <c r="Q75">
-        <v>22.05633851</v>
+        <v>21.92241438</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.176932454133101</v>
+        <v>0.1817466287978587</v>
       </c>
       <c r="T75">
-        <v>2.401736949263463</v>
+        <v>2.489910248916811</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.168917509846398</v>
+        <v>3.126094300253879</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08757302348744328</v>
+        <v>0.08760023435894927</v>
       </c>
       <c r="C76">
-        <v>60.021323749983</v>
+        <v>57.5124009280116</v>
       </c>
       <c r="D76">
-        <v>238.563323749983</v>
+        <v>238.5124009280116</v>
       </c>
       <c r="E76">
-        <v>169.992</v>
+        <v>172.45</v>
       </c>
       <c r="F76">
-        <v>181.892</v>
+        <v>184.35</v>
       </c>
       <c r="G76">
         <v>3.35</v>
@@ -7519,28 +7519,28 @@
         <v>36.448</v>
       </c>
       <c r="M76">
-        <v>11.6592772</v>
+        <v>11.816835</v>
       </c>
       <c r="N76">
-        <v>24.7887228</v>
+        <v>24.631165</v>
       </c>
       <c r="O76">
-        <v>3.71830842</v>
+        <v>3.694674749999999</v>
       </c>
       <c r="P76">
-        <v>21.07041438</v>
+        <v>20.93649025</v>
       </c>
       <c r="Q76">
-        <v>21.92241438</v>
+        <v>21.78849025</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1817466287978587</v>
+        <v>0.1869459374357971</v>
       </c>
       <c r="T76">
-        <v>2.489910248916811</v>
+        <v>2.585137412542426</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.126094300253879</v>
+        <v>3.084413042917159</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08760023435894927</v>
+        <v>0.08762744523045526</v>
       </c>
       <c r="C77">
-        <v>57.5124009280116</v>
+        <v>55.00349984098557</v>
       </c>
       <c r="D77">
-        <v>238.5124009280116</v>
+        <v>238.4614998409856</v>
       </c>
       <c r="E77">
-        <v>172.45</v>
+        <v>174.908</v>
       </c>
       <c r="F77">
-        <v>184.35</v>
+        <v>186.808</v>
       </c>
       <c r="G77">
         <v>3.35</v>
@@ -7601,28 +7601,28 @@
         <v>36.448</v>
       </c>
       <c r="M77">
-        <v>11.816835</v>
+        <v>11.9743928</v>
       </c>
       <c r="N77">
-        <v>24.631165</v>
+        <v>24.4736072</v>
       </c>
       <c r="O77">
-        <v>3.694674749999999</v>
+        <v>3.671041079999999</v>
       </c>
       <c r="P77">
-        <v>20.93649025</v>
+        <v>20.80256612</v>
       </c>
       <c r="Q77">
-        <v>21.78849025</v>
+        <v>21.65456612</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1869459374357971</v>
+        <v>0.1925785217935637</v>
       </c>
       <c r="T77">
-        <v>2.585137412542426</v>
+        <v>2.688300173136842</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.084413042917159</v>
+        <v>3.043828660773513</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08762744523045526</v>
+        <v>0.08765465610196128</v>
       </c>
       <c r="C78">
-        <v>55.00349984098557</v>
+        <v>52.4946204749923</v>
       </c>
       <c r="D78">
-        <v>238.4614998409856</v>
+        <v>238.4106204749923</v>
       </c>
       <c r="E78">
-        <v>174.908</v>
+        <v>177.366</v>
       </c>
       <c r="F78">
-        <v>186.808</v>
+        <v>189.266</v>
       </c>
       <c r="G78">
         <v>3.35</v>
@@ -7683,28 +7683,28 @@
         <v>36.448</v>
       </c>
       <c r="M78">
-        <v>11.9743928</v>
+        <v>12.1319506</v>
       </c>
       <c r="N78">
-        <v>24.4736072</v>
+        <v>24.3160494</v>
       </c>
       <c r="O78">
-        <v>3.671041079999999</v>
+        <v>3.64740741</v>
       </c>
       <c r="P78">
-        <v>20.80256612</v>
+        <v>20.66864199</v>
       </c>
       <c r="Q78">
-        <v>21.65456612</v>
+        <v>21.52064199</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1925785217935637</v>
+        <v>0.1987008960954838</v>
       </c>
       <c r="T78">
-        <v>2.688300173136842</v>
+        <v>2.800433608565555</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.043828660773513</v>
+        <v>3.004298418425805</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08765465610196128</v>
+        <v>0.09285326697346727</v>
       </c>
       <c r="C79">
-        <v>52.4946204749923</v>
+        <v>40.69887678712513</v>
       </c>
       <c r="D79">
-        <v>238.4106204749923</v>
+        <v>229.0728767871252</v>
       </c>
       <c r="E79">
-        <v>177.366</v>
+        <v>179.824</v>
       </c>
       <c r="F79">
-        <v>189.266</v>
+        <v>191.724</v>
       </c>
       <c r="G79">
         <v>3.35</v>
@@ -7765,45 +7765,45 @@
         <v>36.448</v>
       </c>
       <c r="M79">
-        <v>12.1319506</v>
+        <v>13.7849556</v>
       </c>
       <c r="N79">
-        <v>24.3160494</v>
+        <v>22.6630444</v>
       </c>
       <c r="O79">
-        <v>3.64740741</v>
+        <v>3.399456659999999</v>
       </c>
       <c r="P79">
-        <v>20.66864199</v>
+        <v>19.26358774</v>
       </c>
       <c r="Q79">
-        <v>21.52064199</v>
+        <v>20.11558774</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1987008960954838</v>
+        <v>0.2053798498793967</v>
       </c>
       <c r="T79">
-        <v>2.800433608565555</v>
+        <v>2.922760992669605</v>
       </c>
       <c r="U79">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V79">
         <v>0.15</v>
       </c>
       <c r="W79">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y79">
-        <v>3.004298418425805</v>
+        <v>2.644041885778725</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09285326697346727</v>
+        <v>0.09294677784497328</v>
       </c>
       <c r="C80">
-        <v>40.69887678712513</v>
+        <v>38.07960479349182</v>
       </c>
       <c r="D80">
-        <v>229.0728767871252</v>
+        <v>228.9116047934918</v>
       </c>
       <c r="E80">
-        <v>179.824</v>
+        <v>182.282</v>
       </c>
       <c r="F80">
-        <v>191.724</v>
+        <v>194.182</v>
       </c>
       <c r="G80">
         <v>3.35</v>
@@ -7847,28 +7847,28 @@
         <v>36.448</v>
       </c>
       <c r="M80">
-        <v>13.7849556</v>
+        <v>13.9616858</v>
       </c>
       <c r="N80">
-        <v>22.6630444</v>
+        <v>22.4863142</v>
       </c>
       <c r="O80">
-        <v>3.399456659999999</v>
+        <v>3.37294713</v>
       </c>
       <c r="P80">
-        <v>19.26358774</v>
+        <v>19.11336707</v>
       </c>
       <c r="Q80">
-        <v>20.11558774</v>
+        <v>19.96536707</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2053798498793967</v>
+        <v>0.2126948944998728</v>
       </c>
       <c r="T80">
-        <v>2.922760992669605</v>
+        <v>3.056738603831185</v>
       </c>
       <c r="U80">
         <v>0.07190000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.644041885778725</v>
+        <v>2.610573001148615</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09294677784497328</v>
+        <v>0.09304028871647928</v>
       </c>
       <c r="C81">
-        <v>38.07960479349182</v>
+        <v>35.46055971767223</v>
       </c>
       <c r="D81">
-        <v>228.9116047934918</v>
+        <v>228.7505597176722</v>
       </c>
       <c r="E81">
-        <v>182.282</v>
+        <v>184.74</v>
       </c>
       <c r="F81">
-        <v>194.182</v>
+        <v>196.64</v>
       </c>
       <c r="G81">
         <v>3.35</v>
@@ -7929,28 +7929,28 @@
         <v>36.448</v>
       </c>
       <c r="M81">
-        <v>13.9616858</v>
+        <v>14.138416</v>
       </c>
       <c r="N81">
-        <v>22.4863142</v>
+        <v>22.309584</v>
       </c>
       <c r="O81">
-        <v>3.37294713</v>
+        <v>3.346437599999999</v>
       </c>
       <c r="P81">
-        <v>19.11336707</v>
+        <v>18.9631464</v>
       </c>
       <c r="Q81">
-        <v>19.96536707</v>
+        <v>19.8151464</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2126948944998728</v>
+        <v>0.2207414435823964</v>
       </c>
       <c r="T81">
-        <v>3.056738603831185</v>
+        <v>3.204113976108922</v>
       </c>
       <c r="U81">
         <v>0.07190000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.610573001148615</v>
+        <v>2.577940838634257</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09304028871647928</v>
+        <v>0.09313379958798529</v>
       </c>
       <c r="C82">
-        <v>35.46055971767223</v>
+        <v>32.84174108107581</v>
       </c>
       <c r="D82">
-        <v>228.7505597176722</v>
+        <v>228.5897410810758</v>
       </c>
       <c r="E82">
-        <v>184.74</v>
+        <v>187.198</v>
       </c>
       <c r="F82">
-        <v>196.64</v>
+        <v>199.098</v>
       </c>
       <c r="G82">
         <v>3.35</v>
@@ -8011,28 +8011,28 @@
         <v>36.448</v>
       </c>
       <c r="M82">
-        <v>14.138416</v>
+        <v>14.3151462</v>
       </c>
       <c r="N82">
-        <v>22.309584</v>
+        <v>22.1328538</v>
       </c>
       <c r="O82">
-        <v>3.346437599999999</v>
+        <v>3.31992807</v>
       </c>
       <c r="P82">
-        <v>18.9631464</v>
+        <v>18.81292573</v>
       </c>
       <c r="Q82">
-        <v>19.8151464</v>
+        <v>19.66492573</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2207414435823964</v>
+        <v>0.2296349978315015</v>
       </c>
       <c r="T82">
-        <v>3.204113976108922</v>
+        <v>3.367002545468527</v>
       </c>
       <c r="U82">
         <v>0.07190000000000001</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.577940838634257</v>
+        <v>2.546114408527661</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09313379958798529</v>
+        <v>0.09322731045949129</v>
       </c>
       <c r="C83">
-        <v>32.84174108107581</v>
+        <v>30.223148406457</v>
       </c>
       <c r="D83">
-        <v>228.5897410810758</v>
+        <v>228.429148406457</v>
       </c>
       <c r="E83">
-        <v>187.198</v>
+        <v>189.656</v>
       </c>
       <c r="F83">
-        <v>199.098</v>
+        <v>201.556</v>
       </c>
       <c r="G83">
         <v>3.35</v>
@@ -8093,28 +8093,28 @@
         <v>36.448</v>
       </c>
       <c r="M83">
-        <v>14.3151462</v>
+        <v>14.4918764</v>
       </c>
       <c r="N83">
-        <v>22.1328538</v>
+        <v>21.9561236</v>
       </c>
       <c r="O83">
-        <v>3.31992807</v>
+        <v>3.29341854</v>
       </c>
       <c r="P83">
-        <v>18.81292573</v>
+        <v>18.66270506</v>
       </c>
       <c r="Q83">
-        <v>19.66492573</v>
+        <v>19.51470506</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2296349978315015</v>
+        <v>0.2395167247749516</v>
       </c>
       <c r="T83">
-        <v>3.367002545468527</v>
+        <v>3.547989844756976</v>
       </c>
       <c r="U83">
         <v>0.07190000000000001</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.546114408527661</v>
+        <v>2.515064232813909</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09322731045949129</v>
+        <v>0.0960722713309973</v>
       </c>
       <c r="C84">
-        <v>30.223148406457</v>
+        <v>22.98490549989344</v>
       </c>
       <c r="D84">
-        <v>228.429148406457</v>
+        <v>223.6489054998935</v>
       </c>
       <c r="E84">
-        <v>189.656</v>
+        <v>192.114</v>
       </c>
       <c r="F84">
-        <v>201.556</v>
+        <v>204.014</v>
       </c>
       <c r="G84">
         <v>3.35</v>
@@ -8175,45 +8175,45 @@
         <v>36.448</v>
       </c>
       <c r="M84">
-        <v>14.4918764</v>
+        <v>15.4642612</v>
       </c>
       <c r="N84">
-        <v>21.9561236</v>
+        <v>20.9837388</v>
       </c>
       <c r="O84">
-        <v>3.29341854</v>
+        <v>3.147560819999999</v>
       </c>
       <c r="P84">
-        <v>18.66270506</v>
+        <v>17.83617798</v>
       </c>
       <c r="Q84">
-        <v>19.51470506</v>
+        <v>18.68817798</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2395167247749516</v>
+        <v>0.2505610078293959</v>
       </c>
       <c r="T84">
-        <v>3.547989844756976</v>
+        <v>3.750269767491126</v>
       </c>
       <c r="U84">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V84">
         <v>0.15</v>
       </c>
       <c r="W84">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y84">
-        <v>2.515064232813909</v>
+        <v>2.356918285886169</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.0960722713309973</v>
+        <v>0.09619893220250329</v>
       </c>
       <c r="C85">
-        <v>22.98490549989344</v>
+        <v>20.31873127163249</v>
       </c>
       <c r="D85">
-        <v>223.6489054998935</v>
+        <v>223.4407312716325</v>
       </c>
       <c r="E85">
-        <v>192.114</v>
+        <v>194.572</v>
       </c>
       <c r="F85">
-        <v>204.014</v>
+        <v>206.472</v>
       </c>
       <c r="G85">
         <v>3.35</v>
@@ -8257,28 +8257,28 @@
         <v>36.448</v>
       </c>
       <c r="M85">
-        <v>15.4642612</v>
+        <v>15.6505776</v>
       </c>
       <c r="N85">
-        <v>20.9837388</v>
+        <v>20.79742239999999</v>
       </c>
       <c r="O85">
-        <v>3.147560819999999</v>
+        <v>3.119613359999999</v>
       </c>
       <c r="P85">
-        <v>17.83617798</v>
+        <v>17.67780904</v>
       </c>
       <c r="Q85">
-        <v>18.68817798</v>
+        <v>18.52980904</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2505610078293959</v>
+        <v>0.2629858262656457</v>
       </c>
       <c r="T85">
-        <v>3.750269767491126</v>
+        <v>3.977834680567045</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.356918285886169</v>
+        <v>2.328859734863714</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09619893220250329</v>
+        <v>0.09632559307400929</v>
       </c>
       <c r="C86">
-        <v>20.31873127163252</v>
+        <v>17.65294422352568</v>
       </c>
       <c r="D86">
-        <v>223.4407312716325</v>
+        <v>223.2329442235257</v>
       </c>
       <c r="E86">
-        <v>194.572</v>
+        <v>197.03</v>
       </c>
       <c r="F86">
-        <v>206.472</v>
+        <v>208.93</v>
       </c>
       <c r="G86">
         <v>3.35</v>
@@ -8339,28 +8339,28 @@
         <v>36.448</v>
       </c>
       <c r="M86">
-        <v>15.6505776</v>
+        <v>15.836894</v>
       </c>
       <c r="N86">
-        <v>20.7974224</v>
+        <v>20.611106</v>
       </c>
       <c r="O86">
-        <v>3.11961336</v>
+        <v>3.0916659</v>
       </c>
       <c r="P86">
-        <v>17.67780904</v>
+        <v>17.5194401</v>
       </c>
       <c r="Q86">
-        <v>18.52980904</v>
+        <v>18.3714401</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2629858262656455</v>
+        <v>0.2770672871600619</v>
       </c>
       <c r="T86">
-        <v>3.977834680567042</v>
+        <v>4.235741582053082</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.328859734863715</v>
+        <v>2.301461385041789</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09632559307400929</v>
+        <v>0.09645225394551529</v>
       </c>
       <c r="C87">
-        <v>17.65294422352568</v>
+        <v>14.98754327641055</v>
       </c>
       <c r="D87">
-        <v>223.2329442235257</v>
+        <v>223.0255432764106</v>
       </c>
       <c r="E87">
-        <v>197.03</v>
+        <v>199.488</v>
       </c>
       <c r="F87">
-        <v>208.93</v>
+        <v>211.388</v>
       </c>
       <c r="G87">
         <v>3.35</v>
@@ -8421,28 +8421,28 @@
         <v>36.448</v>
       </c>
       <c r="M87">
-        <v>15.836894</v>
+        <v>16.0232104</v>
       </c>
       <c r="N87">
-        <v>20.611106</v>
+        <v>20.4247896</v>
       </c>
       <c r="O87">
-        <v>3.0916659</v>
+        <v>3.06371844</v>
       </c>
       <c r="P87">
-        <v>17.5194401</v>
+        <v>17.36107116</v>
       </c>
       <c r="Q87">
-        <v>18.3714401</v>
+        <v>18.21307116</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2770672871600619</v>
+        <v>0.2931603853251091</v>
       </c>
       <c r="T87">
-        <v>4.235741582053082</v>
+        <v>4.530492326608556</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.301461385041789</v>
+        <v>2.274700206145955</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09645225394551529</v>
+        <v>0.0965789148170213</v>
       </c>
       <c r="C88">
-        <v>14.98754327641055</v>
+        <v>12.32252735513157</v>
       </c>
       <c r="D88">
-        <v>223.0255432764106</v>
+        <v>222.8185273551316</v>
       </c>
       <c r="E88">
-        <v>199.488</v>
+        <v>201.946</v>
       </c>
       <c r="F88">
-        <v>211.388</v>
+        <v>213.846</v>
       </c>
       <c r="G88">
         <v>3.35</v>
@@ -8503,28 +8503,28 @@
         <v>36.448</v>
       </c>
       <c r="M88">
-        <v>16.0232104</v>
+        <v>16.2095268</v>
       </c>
       <c r="N88">
-        <v>20.4247896</v>
+        <v>20.2384732</v>
       </c>
       <c r="O88">
-        <v>3.06371844</v>
+        <v>3.03577098</v>
       </c>
       <c r="P88">
-        <v>17.36107116</v>
+        <v>17.20270222</v>
       </c>
       <c r="Q88">
-        <v>18.21307116</v>
+        <v>18.05470222</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2931603853251091</v>
+        <v>0.3117293447463176</v>
       </c>
       <c r="T88">
-        <v>4.530492326608556</v>
+        <v>4.87058933955718</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.274700206145955</v>
+        <v>2.248554226764966</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.0965789148170213</v>
+        <v>0.09670557568852731</v>
       </c>
       <c r="C89">
-        <v>12.32252735513157</v>
+        <v>9.657895388521354</v>
       </c>
       <c r="D89">
-        <v>222.8185273551316</v>
+        <v>222.6118953885214</v>
       </c>
       <c r="E89">
-        <v>201.946</v>
+        <v>204.404</v>
       </c>
       <c r="F89">
-        <v>213.846</v>
+        <v>216.304</v>
       </c>
       <c r="G89">
         <v>3.35</v>
@@ -8585,28 +8585,28 @@
         <v>36.448</v>
       </c>
       <c r="M89">
-        <v>16.2095268</v>
+        <v>16.3958432</v>
       </c>
       <c r="N89">
-        <v>20.2384732</v>
+        <v>20.0521568</v>
       </c>
       <c r="O89">
-        <v>3.03577098</v>
+        <v>3.00782352</v>
       </c>
       <c r="P89">
-        <v>17.20270222</v>
+        <v>17.04433328</v>
       </c>
       <c r="Q89">
-        <v>18.05470222</v>
+        <v>17.89633328</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3117293447463176</v>
+        <v>0.3333931307377275</v>
       </c>
       <c r="T89">
-        <v>4.87058933955718</v>
+        <v>5.267369187997243</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.248554226764966</v>
+        <v>2.223002474188092</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09670557568852731</v>
+        <v>0.09683223656003329</v>
       </c>
       <c r="C90">
-        <v>9.657895388521354</v>
+        <v>6.993646309382314</v>
       </c>
       <c r="D90">
-        <v>222.6118953885214</v>
+        <v>222.4056463093823</v>
       </c>
       <c r="E90">
-        <v>204.404</v>
+        <v>206.862</v>
       </c>
       <c r="F90">
-        <v>216.304</v>
+        <v>218.762</v>
       </c>
       <c r="G90">
         <v>3.35</v>
@@ -8667,28 +8667,28 @@
         <v>36.448</v>
       </c>
       <c r="M90">
-        <v>16.3958432</v>
+        <v>16.5821596</v>
       </c>
       <c r="N90">
-        <v>20.0521568</v>
+        <v>19.8658404</v>
       </c>
       <c r="O90">
-        <v>3.00782352</v>
+        <v>2.97987606</v>
       </c>
       <c r="P90">
-        <v>17.04433328</v>
+        <v>16.88596434</v>
       </c>
       <c r="Q90">
-        <v>17.89633328</v>
+        <v>17.73796434</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3333931307377275</v>
+        <v>0.3589957869093936</v>
       </c>
       <c r="T90">
-        <v>5.267369187997243</v>
+        <v>5.736290827062771</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.223002474188092</v>
+        <v>2.198024918298338</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09683223656003329</v>
+        <v>0.09695889743153929</v>
       </c>
       <c r="C91">
-        <v>6.993646309382314</v>
+        <v>4.32977905446802</v>
       </c>
       <c r="D91">
-        <v>222.4056463093823</v>
+        <v>222.1997790544681</v>
       </c>
       <c r="E91">
-        <v>206.862</v>
+        <v>209.32</v>
       </c>
       <c r="F91">
-        <v>218.762</v>
+        <v>221.22</v>
       </c>
       <c r="G91">
         <v>3.35</v>
@@ -8749,28 +8749,28 @@
         <v>36.448</v>
       </c>
       <c r="M91">
-        <v>16.5821596</v>
+        <v>16.768476</v>
       </c>
       <c r="N91">
-        <v>19.8658404</v>
+        <v>19.679524</v>
       </c>
       <c r="O91">
-        <v>2.97987606</v>
+        <v>2.9519286</v>
       </c>
       <c r="P91">
-        <v>16.88596434</v>
+        <v>16.7275954</v>
       </c>
       <c r="Q91">
-        <v>17.73796434</v>
+        <v>17.5795954</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3589957869093936</v>
+        <v>0.389718974315393</v>
       </c>
       <c r="T91">
-        <v>5.736290827062771</v>
+        <v>6.298996793941405</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.198024918298338</v>
+        <v>2.173602419206134</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09695889743153929</v>
+        <v>0.0970855583030453</v>
       </c>
       <c r="C92">
-        <v>4.32977905446802</v>
+        <v>1.666292564465408</v>
       </c>
       <c r="D92">
-        <v>222.1997790544681</v>
+        <v>221.9942925644654</v>
       </c>
       <c r="E92">
-        <v>209.32</v>
+        <v>211.778</v>
       </c>
       <c r="F92">
-        <v>221.22</v>
+        <v>223.678</v>
       </c>
       <c r="G92">
         <v>3.35</v>
@@ -8831,28 +8831,28 @@
         <v>36.448</v>
       </c>
       <c r="M92">
-        <v>16.768476</v>
+        <v>16.9547924</v>
       </c>
       <c r="N92">
-        <v>19.679524</v>
+        <v>19.4932076</v>
       </c>
       <c r="O92">
-        <v>2.9519286</v>
+        <v>2.92398114</v>
       </c>
       <c r="P92">
-        <v>16.7275954</v>
+        <v>16.56922646</v>
       </c>
       <c r="Q92">
-        <v>17.5795954</v>
+        <v>17.42122646</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.389718974315393</v>
+        <v>0.4272695367005034</v>
       </c>
       <c r="T92">
-        <v>6.298996793941405</v>
+        <v>6.986748531237512</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.173602419206134</v>
+        <v>2.149716678335737</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.0970855583030453</v>
+        <v>0.09721221917455131</v>
       </c>
       <c r="C93">
-        <v>1.666292564465408</v>
+        <v>-0.9968142160238358</v>
       </c>
       <c r="D93">
-        <v>221.9942925644654</v>
+        <v>221.7891857839762</v>
       </c>
       <c r="E93">
-        <v>211.778</v>
+        <v>214.236</v>
       </c>
       <c r="F93">
-        <v>223.678</v>
+        <v>226.136</v>
       </c>
       <c r="G93">
         <v>3.35</v>
@@ -8913,28 +8913,28 @@
         <v>36.448</v>
       </c>
       <c r="M93">
-        <v>16.9547924</v>
+        <v>17.1411088</v>
       </c>
       <c r="N93">
-        <v>19.4932076</v>
+        <v>19.3068912</v>
       </c>
       <c r="O93">
-        <v>2.92398114</v>
+        <v>2.896033679999999</v>
       </c>
       <c r="P93">
-        <v>16.56922646</v>
+        <v>16.41085752</v>
       </c>
       <c r="Q93">
-        <v>17.42122646</v>
+        <v>17.26285752</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4272695367005034</v>
+        <v>0.4742077396818914</v>
       </c>
       <c r="T93">
-        <v>6.986748531237512</v>
+        <v>7.846438202857648</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.149716678335737</v>
+        <v>2.126350192701652</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09721221917455131</v>
+        <v>0.0973388800460573</v>
       </c>
       <c r="C94">
-        <v>-0.9968142160238358</v>
+        <v>-3.659542338501154</v>
       </c>
       <c r="D94">
-        <v>221.7891857839762</v>
+        <v>221.5844576614989</v>
       </c>
       <c r="E94">
-        <v>214.236</v>
+        <v>216.694</v>
       </c>
       <c r="F94">
-        <v>226.136</v>
+        <v>228.594</v>
       </c>
       <c r="G94">
         <v>3.35</v>
@@ -8995,28 +8995,28 @@
         <v>36.448</v>
       </c>
       <c r="M94">
-        <v>17.1411088</v>
+        <v>17.3274252</v>
       </c>
       <c r="N94">
-        <v>19.3068912</v>
+        <v>19.1205748</v>
       </c>
       <c r="O94">
-        <v>2.896033679999999</v>
+        <v>2.868086219999999</v>
       </c>
       <c r="P94">
-        <v>16.41085752</v>
+        <v>16.25248858</v>
       </c>
       <c r="Q94">
-        <v>17.26285752</v>
+        <v>17.10448858</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4742077396818914</v>
+        <v>0.5345568578008189</v>
       </c>
       <c r="T94">
-        <v>7.846438202857648</v>
+        <v>8.951753494940679</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.126350192701652</v>
+        <v>2.103486212134968</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.0973388800460573</v>
+        <v>0.09746554091756329</v>
       </c>
       <c r="C95">
-        <v>-3.659542338501154</v>
+        <v>-6.321892850589109</v>
       </c>
       <c r="D95">
-        <v>221.5844576614989</v>
+        <v>221.3801071494109</v>
       </c>
       <c r="E95">
-        <v>216.694</v>
+        <v>219.152</v>
       </c>
       <c r="F95">
-        <v>228.594</v>
+        <v>231.052</v>
       </c>
       <c r="G95">
         <v>3.35</v>
@@ -9077,28 +9077,28 @@
         <v>36.448</v>
       </c>
       <c r="M95">
-        <v>17.3274252</v>
+        <v>17.5137416</v>
       </c>
       <c r="N95">
-        <v>19.1205748</v>
+        <v>18.9342584</v>
       </c>
       <c r="O95">
-        <v>2.868086219999999</v>
+        <v>2.840138759999999</v>
       </c>
       <c r="P95">
-        <v>16.25248858</v>
+        <v>16.09411964</v>
       </c>
       <c r="Q95">
-        <v>17.10448858</v>
+        <v>16.94611964</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5345568578008189</v>
+        <v>0.6150223486260554</v>
       </c>
       <c r="T95">
-        <v>8.951753494940679</v>
+        <v>10.42550721771805</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.103486212134968</v>
+        <v>2.081108699239915</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09746554091756329</v>
+        <v>0.0975922017890693</v>
       </c>
       <c r="C96">
-        <v>-6.321892850589109</v>
+        <v>-8.983866796049284</v>
       </c>
       <c r="D96">
-        <v>221.3801071494109</v>
+        <v>221.1761332039507</v>
       </c>
       <c r="E96">
-        <v>219.152</v>
+        <v>221.61</v>
       </c>
       <c r="F96">
-        <v>231.052</v>
+        <v>233.51</v>
       </c>
       <c r="G96">
         <v>3.35</v>
@@ -9159,28 +9159,28 @@
         <v>36.448</v>
       </c>
       <c r="M96">
-        <v>17.5137416</v>
+        <v>17.700058</v>
       </c>
       <c r="N96">
-        <v>18.9342584</v>
+        <v>18.747942</v>
       </c>
       <c r="O96">
-        <v>2.840138759999999</v>
+        <v>2.8121913</v>
       </c>
       <c r="P96">
-        <v>16.09411964</v>
+        <v>15.9357507</v>
       </c>
       <c r="Q96">
-        <v>16.94611964</v>
+        <v>16.7877507</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6150223486260554</v>
+        <v>0.7276740357813869</v>
       </c>
       <c r="T96">
-        <v>10.42550721771805</v>
+        <v>12.48876242960638</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.081108699239915</v>
+        <v>2.059202291879495</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.0975922017890693</v>
+        <v>0.09771886266057531</v>
       </c>
       <c r="C97">
-        <v>-8.983866796049284</v>
+        <v>-11.64546521479991</v>
       </c>
       <c r="D97">
-        <v>221.1761332039507</v>
+        <v>220.9725347852001</v>
       </c>
       <c r="E97">
-        <v>221.61</v>
+        <v>224.068</v>
       </c>
       <c r="F97">
-        <v>233.51</v>
+        <v>235.968</v>
       </c>
       <c r="G97">
         <v>3.35</v>
@@ -9241,28 +9241,28 @@
         <v>36.448</v>
       </c>
       <c r="M97">
-        <v>17.700058</v>
+        <v>17.8863744</v>
       </c>
       <c r="N97">
-        <v>18.747942</v>
+        <v>18.5616256</v>
       </c>
       <c r="O97">
-        <v>2.8121913</v>
+        <v>2.78424384</v>
       </c>
       <c r="P97">
-        <v>15.9357507</v>
+        <v>15.77738176</v>
       </c>
       <c r="Q97">
-        <v>16.7877507</v>
+        <v>16.62938176</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7276740357813869</v>
+        <v>0.896651566514384</v>
       </c>
       <c r="T97">
-        <v>12.48876242960638</v>
+        <v>15.58364524743888</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.059202291879495</v>
+        <v>2.037752268005751</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09771886266057531</v>
+        <v>0.09784552353208131</v>
       </c>
       <c r="C98">
-        <v>-11.64546521479988</v>
+        <v>-14.30668914293381</v>
       </c>
       <c r="D98">
-        <v>220.9725347852001</v>
+        <v>220.7693108570662</v>
       </c>
       <c r="E98">
-        <v>224.068</v>
+        <v>226.526</v>
       </c>
       <c r="F98">
-        <v>235.968</v>
+        <v>238.426</v>
       </c>
       <c r="G98">
         <v>3.35</v>
@@ -9323,28 +9323,28 @@
         <v>36.448</v>
       </c>
       <c r="M98">
-        <v>17.8863744</v>
+        <v>18.0726908</v>
       </c>
       <c r="N98">
-        <v>18.5616256</v>
+        <v>18.3753092</v>
       </c>
       <c r="O98">
-        <v>2.78424384</v>
+        <v>2.756296379999999</v>
       </c>
       <c r="P98">
-        <v>15.77738176</v>
+        <v>15.61901282</v>
       </c>
       <c r="Q98">
-        <v>16.62938176</v>
+        <v>16.47101282</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8966515665143818</v>
+        <v>1.178280784402709</v>
       </c>
       <c r="T98">
-        <v>15.58364524743883</v>
+        <v>20.74178327715963</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.037752268005751</v>
+        <v>2.016744512665485</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09784552353208131</v>
+        <v>0.1098007844035873</v>
       </c>
       <c r="C99">
-        <v>-14.30668914293381</v>
+        <v>-34.39823020842385</v>
       </c>
       <c r="D99">
-        <v>220.7693108570662</v>
+        <v>203.1357697915762</v>
       </c>
       <c r="E99">
-        <v>226.526</v>
+        <v>228.984</v>
       </c>
       <c r="F99">
-        <v>238.426</v>
+        <v>240.884</v>
       </c>
       <c r="G99">
         <v>3.35</v>
@@ -9405,45 +9405,45 @@
         <v>36.448</v>
       </c>
       <c r="M99">
-        <v>18.0726908</v>
+        <v>21.67956</v>
       </c>
       <c r="N99">
-        <v>18.3753092</v>
+        <v>14.76844</v>
       </c>
       <c r="O99">
-        <v>2.756296379999999</v>
+        <v>2.215266</v>
       </c>
       <c r="P99">
-        <v>15.61901282</v>
+        <v>12.553174</v>
       </c>
       <c r="Q99">
-        <v>16.47101282</v>
+        <v>13.405174</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.178280784402709</v>
+        <v>1.741539220179364</v>
       </c>
       <c r="T99">
-        <v>20.74178327715963</v>
+        <v>31.05805933660123</v>
       </c>
       <c r="U99">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V99">
         <v>0.15</v>
       </c>
       <c r="W99">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y99">
-        <v>2.016744512665485</v>
+        <v>1.681214932406377</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1098007844035873</v>
+        <v>0.1100481452750933</v>
       </c>
       <c r="C100">
-        <v>-34.39823020842385</v>
+        <v>-37.19138238954443</v>
       </c>
       <c r="D100">
-        <v>203.1357697915762</v>
+        <v>202.8006176104556</v>
       </c>
       <c r="E100">
-        <v>228.984</v>
+        <v>231.442</v>
       </c>
       <c r="F100">
-        <v>240.884</v>
+        <v>243.342</v>
       </c>
       <c r="G100">
         <v>3.35</v>
@@ -9487,28 +9487,28 @@
         <v>36.448</v>
       </c>
       <c r="M100">
-        <v>21.67956</v>
+        <v>21.90078</v>
       </c>
       <c r="N100">
-        <v>14.76844</v>
+        <v>14.54722</v>
       </c>
       <c r="O100">
-        <v>2.215266</v>
+        <v>2.182083</v>
       </c>
       <c r="P100">
-        <v>12.553174</v>
+        <v>12.365137</v>
       </c>
       <c r="Q100">
-        <v>13.405174</v>
+        <v>13.217137</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.741539220179364</v>
+        <v>3.431314527509327</v>
       </c>
       <c r="T100">
-        <v>31.05805933660123</v>
+        <v>62.00688751492601</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.681214932406377</v>
+        <v>1.664232963392172</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1100481452750933</v>
-      </c>
-      <c r="C101">
-        <v>-37.19138238954443</v>
-      </c>
-      <c r="D101">
-        <v>202.8006176104556</v>
-      </c>
-      <c r="E101">
-        <v>231.442</v>
-      </c>
-      <c r="F101">
-        <v>243.342</v>
-      </c>
-      <c r="G101">
-        <v>3.35</v>
-      </c>
-      <c r="H101">
-        <v>233.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>37.3</v>
-      </c>
-      <c r="K101">
-        <v>0.852</v>
-      </c>
-      <c r="L101">
-        <v>36.448</v>
-      </c>
-      <c r="M101">
-        <v>21.90078</v>
-      </c>
-      <c r="N101">
-        <v>14.54722</v>
-      </c>
-      <c r="O101">
-        <v>2.182083</v>
-      </c>
-      <c r="P101">
-        <v>12.365137</v>
-      </c>
-      <c r="Q101">
-        <v>13.217137</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.431314527509327</v>
-      </c>
-      <c r="T101">
-        <v>62.00688751492601</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.15</v>
-      </c>
-      <c r="W101">
-        <v>0.0765</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.664232963392172</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
